--- a/Datasets/extra-files/dataset_table.xlsx
+++ b/Datasets/extra-files/dataset_table.xlsx
@@ -34,7 +34,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -49,92 +49,98 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00AFE8F9"/>
-        <bgColor rgb="00AFE8F9"/>
+        <fgColor rgb="00AFE9F9"/>
+        <bgColor rgb="00AFE9F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A9DDF9"/>
-        <bgColor rgb="00A9DDF9"/>
+        <fgColor rgb="00A9DEF9"/>
+        <bgColor rgb="00A9DEF9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A3D2FA"/>
-        <bgColor rgb="00A3D2FA"/>
+        <fgColor rgb="00A4D4FA"/>
+        <bgColor rgb="00A4D4FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009DC7FA"/>
-        <bgColor rgb="009DC7FA"/>
+        <fgColor rgb="009EC9FA"/>
+        <bgColor rgb="009EC9FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0096BCFA"/>
-        <bgColor rgb="0096BCFA"/>
+        <fgColor rgb="0098BFFA"/>
+        <bgColor rgb="0098BFFA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0090B1FA"/>
-        <bgColor rgb="0090B1FA"/>
+        <fgColor rgb="0092B4FA"/>
+        <bgColor rgb="0092B4FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008AA6FB"/>
-        <bgColor rgb="008AA6FB"/>
+        <fgColor rgb="008DAAFB"/>
+        <bgColor rgb="008DAAFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00849BFB"/>
-        <bgColor rgb="00849BFB"/>
+        <fgColor rgb="00879FFB"/>
+        <bgColor rgb="00879FFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008395F9"/>
-        <bgColor rgb="008395F9"/>
+        <fgColor rgb="008195FB"/>
+        <bgColor rgb="008195FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008796F6"/>
-        <bgColor rgb="008796F6"/>
+        <fgColor rgb="008596F8"/>
+        <bgColor rgb="008596F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008C97F3"/>
-        <bgColor rgb="008C97F3"/>
+        <fgColor rgb="008997F5"/>
+        <bgColor rgb="008997F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009098EF"/>
-        <bgColor rgb="009098EF"/>
+        <fgColor rgb="008D98F2"/>
+        <bgColor rgb="008D98F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009499EC"/>
-        <bgColor rgb="009499EC"/>
+        <fgColor rgb="009199EF"/>
+        <bgColor rgb="009199EF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00989AE9"/>
-        <bgColor rgb="00989AE9"/>
+        <fgColor rgb="009599EB"/>
+        <bgColor rgb="009599EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009D9BE6"/>
-        <bgColor rgb="009D9BE6"/>
+        <fgColor rgb="00999AE8"/>
+        <bgColor rgb="00999AE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009D9BE5"/>
+        <bgColor rgb="009D9BE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -168,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -225,12 +231,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -319,9 +328,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Datasets" displayName="Datasets" ref="A1:R38" headerRowCount="1">
-  <autoFilter ref="A1:R38"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Datasets" displayName="Datasets" ref="A1:S38" headerRowCount="1">
+  <autoFilter ref="A1:S38"/>
+  <tableColumns count="19">
     <tableColumn id="1" name="Dataset"/>
     <tableColumn id="2" name="Summary"/>
     <tableColumn id="3" name="Features"/>
@@ -329,17 +338,18 @@
     <tableColumn id="5" name="Camera Model"/>
     <tableColumn id="6" name="Web"/>
     <tableColumn id="7" name="Publication"/>
-    <tableColumn id="8" name="Year"/>
-    <tableColumn id="9" name="Authors"/>
-    <tableColumn id="10" name="BibTeX Key"/>
-    <tableColumn id="11" name="BibTeX"/>
-    <tableColumn id="12" name="Maintainer"/>
-    <tableColumn id="13" name="AI-Assisted"/>
-    <tableColumn id="14" name="Raw Format"/>
-    <tableColumn id="15" name="Download"/>
-    <tableColumn id="16" name="Download Issues"/>
-    <tableColumn id="17" name="Access"/>
-    <tableColumn id="18" name="License"/>
+    <tableColumn id="8" name="Publication URL"/>
+    <tableColumn id="9" name="Year"/>
+    <tableColumn id="10" name="Authors"/>
+    <tableColumn id="11" name="BibTeX Key"/>
+    <tableColumn id="12" name="BibTeX"/>
+    <tableColumn id="13" name="Maintainer"/>
+    <tableColumn id="14" name="AI-Assisted"/>
+    <tableColumn id="15" name="Raw Format"/>
+    <tableColumn id="16" name="Download"/>
+    <tableColumn id="17" name="Download Issues"/>
+    <tableColumn id="18" name="Access"/>
+    <tableColumn id="19" name="License"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0"/>
 </table>
@@ -634,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -655,6 +665,7 @@
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="20" customWidth="1" min="17" max="17"/>
     <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -695,2599 +706,3529 @@
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
+          <t>Publication URL</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>Authors</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>BibTeX Key</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>BibTeX</t>
         </is>
       </c>
-      <c r="L1" s="12" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>Maintainer</t>
         </is>
       </c>
-      <c r="M1" s="13" t="inlineStr">
+      <c r="N1" s="14" t="inlineStr">
         <is>
           <t>AI-Assisted</t>
         </is>
       </c>
-      <c r="N1" s="14" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>Raw Format</t>
         </is>
       </c>
-      <c r="O1" s="15" t="inlineStr">
+      <c r="P1" s="16" t="inlineStr">
         <is>
           <t>Download</t>
         </is>
       </c>
-      <c r="P1" s="16" t="inlineStr">
+      <c r="Q1" s="17" t="inlineStr">
         <is>
           <t>Download Issues</t>
         </is>
       </c>
-      <c r="Q1" s="17" t="inlineStr">
+      <c r="R1" s="18" t="inlineStr">
         <is>
           <t>Access</t>
         </is>
       </c>
-      <c r="R1" s="18" t="inlineStr">
+      <c r="S1" s="19" t="inlineStr">
         <is>
           <t>License</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>7scenes</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>Tracked RGB-D Kinect frames from seven indoor scenes, for camera relocalization/SLAM research</t>
         </is>
       </c>
-      <c r="C2" s="20" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>📸🏠🤳</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>mono, rgbd</t>
         </is>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>https://www.microsoft.com/en-us/research/project/rgb-d-dataset-7-scenes/</t>
         </is>
       </c>
-      <c r="G2" s="20" t="inlineStr"/>
-      <c r="H2" s="20" t="inlineStr"/>
-      <c r="I2" s="20" t="inlineStr">
+      <c r="G2" s="21" t="inlineStr">
+        <is>
+          <t>Real-time RGB-D camera relocalization</t>
+        </is>
+      </c>
+      <c r="H2" s="22" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/abstract/document/6671777</t>
+        </is>
+      </c>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="J2" s="21" t="inlineStr">
         <is>
           <t>Jamie Shotton, Ben Glocker, Christopher Zach, Shahram Izadi, Antonio Criminisi, Andrew Fitzgibbon</t>
         </is>
       </c>
-      <c r="J2" s="20" t="inlineStr"/>
-      <c r="K2" s="20" t="inlineStr"/>
-      <c r="L2" s="20" t="inlineStr">
+      <c r="K2" s="21" t="inlineStr">
+        <is>
+          <t>glocker2013real</t>
+        </is>
+      </c>
+      <c r="L2" s="21" t="inlineStr">
+        <is>
+          <t>@inproceedings{glocker2013real,   title={Real-time RGB-D camera relocalization},   author={Glocker, Ben and Izadi, Shahram and Shotton, Jamie and Criminisi, Antonio},   booktitle={2013 IEEE International Symposium on Mixed and Augmented Reality (ISMAR)},   pages={173--179},   year={2013},   organization={IEEE} }</t>
+        </is>
+      </c>
+      <c r="M2" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M2" s="20" t="inlineStr">
+      <c r="N2" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N2" s="20" t="inlineStr">
+      <c r="O2" s="21" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O2" s="20" t="inlineStr">
+      <c r="P2" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P2" s="20" t="inlineStr"/>
-      <c r="Q2" s="20" t="inlineStr"/>
-      <c r="R2" s="20" t="inlineStr">
+      <c r="Q2" s="21" t="inlineStr"/>
+      <c r="R2" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S2" s="21" t="inlineStr">
         <is>
           <t>Non-commercial use only (custom Microsoft Research license agreement)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>ariel</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Multi-Camera Underwater Visual-Inertial Dataset - a BlueROV2-based platform (Ariel) surveying a Norwegian fjord and an indoor test tank</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>📸🏠🏞️🌊🤖</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>mono, mono-vi, stereo, stereo-vi</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>equid4</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="25" t="inlineStr">
         <is>
           <t>https://huggingface.co/datasets/ntnu-arl/underwater-datasets</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr"/>
-      <c r="H3" s="23" t="inlineStr"/>
-      <c r="I3" s="23" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>An Online Self-calibrating Refractive Camera Model with Application to Underwater Odometry</t>
+        </is>
+      </c>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2310.16658</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="J3" s="24" t="inlineStr">
         <is>
           <t>Mohit Singh, Mihir Dharmadhikari, Kostas Alexis</t>
         </is>
       </c>
-      <c r="J3" s="23" t="inlineStr"/>
-      <c r="K3" s="23" t="inlineStr"/>
-      <c r="L3" s="23" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>singh2023online</t>
+        </is>
+      </c>
+      <c r="L3" s="24" t="inlineStr">
+        <is>
+          <t>@misc{singh2023online,       title={An Online Self-calibrating Refractive Camera Model with Application to Underwater Odometry},        author={Mohit Singh and Mihir Dharmadhikari and Kostas Alexis},       year={2023},       eprint={2310.16658},       archivePrefix={arXiv},       primaryClass={cs.RO} }</t>
+        </is>
+      </c>
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M3" s="23" t="inlineStr">
+      <c r="N3" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N3" s="23" t="inlineStr">
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t>ros1</t>
         </is>
       </c>
-      <c r="O3" s="23" t="inlineStr">
+      <c r="P3" s="24" t="inlineStr">
         <is>
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="P3" s="23" t="inlineStr"/>
-      <c r="Q3" s="23" t="inlineStr"/>
-      <c r="R3" s="23" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr"/>
+      <c r="R3" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S3" s="24" t="inlineStr">
         <is>
           <t>BSD-3-Clause</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>caves</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>Underwater Caves Sonar and Vision Data Set - a diver-guided AUV exploration of an underwater cave complex, with sonar, DVL, dual-IMU and vertically-mounted camera data</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t>📸🏞️🌊</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>mono</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>https://cirs.udg.edu/caves-dataset/</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr"/>
-      <c r="H4" s="20" t="inlineStr"/>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Underwater caves sonar data set</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>https://journals.sagepub.com/doi/10.1177/0278364917732838</t>
+        </is>
+      </c>
+      <c r="I4" s="21" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t>Angelos Mallios, Eduard Vidal, Ricard Campos, Marc Carreras</t>
         </is>
       </c>
-      <c r="J4" s="20" t="inlineStr"/>
-      <c r="K4" s="20" t="inlineStr"/>
-      <c r="L4" s="20" t="inlineStr">
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>mallios2017underwater</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t>@article{mallios2017underwater,   title={Underwater caves sonar data set},   author={Mallios, Angelos and Vidal, Eduard and Campos, Ricard and Carreras, Marc},   journal={The International Journal of Robotics Research},   volume={36},   number={12},   pages={1247--1251},   year={2017},   publisher={Sage Publications Sage UK: London, England} }</t>
+        </is>
+      </c>
+      <c r="M4" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M4" s="20" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N4" s="20" t="inlineStr">
+      <c r="O4" s="21" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O4" s="20" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P4" s="20" t="inlineStr"/>
-      <c r="Q4" s="20" t="inlineStr"/>
-      <c r="R4" s="20" t="inlineStr">
+      <c r="Q4" s="21" t="inlineStr"/>
+      <c r="R4" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S4" s="21" t="inlineStr">
         <is>
           <t>CC BY-NC-SA 4.0</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>drunkards</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>The Drunkard's Dataset - synthetic RGB-D exploratory camera trajectories with ground truth in non-rigidly deforming indoor scenes</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>💻🏠🤳</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>mono, rgbd</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>https://davidrecasens.github.io/TheDrunkard'sOdometry/</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr"/>
-      <c r="H5" s="23" t="inlineStr"/>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>The Drunkard's Odometry: Estimating Camera Motion in Deforming Scenes</t>
+        </is>
+      </c>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>https://proceedings.neurips.cc/paper_files/paper/2023/hash/98c9b79e9c686aadd4d81e34a7773dd1-Abstract-Datasets_and_Benchmarks.html</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="J5" s="24" t="inlineStr">
         <is>
           <t>David Recasens, Martin R. Oswald, Marc Pollefeys, Javier Civera</t>
         </is>
       </c>
-      <c r="J5" s="23" t="inlineStr"/>
-      <c r="K5" s="23" t="inlineStr"/>
-      <c r="L5" s="23" t="inlineStr">
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>recasens2024drunkard</t>
+        </is>
+      </c>
+      <c r="L5" s="24" t="inlineStr">
+        <is>
+          <t>@article{recasens2024drunkard,   title={The Drunkard’s Odometry: Estimating Camera Motion in Deforming Scenes},   author={Recasens Lafuente, David and Oswald, Martin R and Pollefeys, Marc and Civera, Javier},   journal={Advances in Neural Information Processing Systems},   volume={36},   year={2024} }</t>
+        </is>
+      </c>
+      <c r="M5" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M5" s="23" t="inlineStr">
+      <c r="N5" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N5" s="23" t="inlineStr">
+      <c r="O5" s="24" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O5" s="23" t="inlineStr">
+      <c r="P5" s="24" t="inlineStr">
         <is>
           <t>google-drive</t>
         </is>
       </c>
-      <c r="P5" s="23" t="inlineStr"/>
-      <c r="Q5" s="23" t="inlineStr"/>
-      <c r="R5" s="23" t="inlineStr">
+      <c r="Q5" s="24" t="inlineStr"/>
+      <c r="R5" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S5" s="24" t="inlineStr">
         <is>
           <t>MIT License (some components subject to their original licenses)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>eiffel-tower</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Deep-sea hydrothermal vent imagery from four ROV Victor6000 survey campaigns (2015-2020) of the Eiffel Tower edifice, with per-campaign COLMAP poses for long-term visual localization</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>📸🏞️🌊🤖</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>mono</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>radtan4</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>https://www.seanoe.org/data/00810/92226/</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>Eiffel Tower: A deep-sea underwater dataset for long-term visual localization</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/02783649231177322</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t>Clémentin Boittiaux, Claire Dune, Maxime Ferrera, Aurélien Arnaubec, Ricard Marxer, Marjolaine Matabos, Loïc Van Audenhaege, Vincent Hugel</t>
         </is>
       </c>
-      <c r="J6" s="20" t="inlineStr"/>
-      <c r="K6" s="20" t="inlineStr"/>
-      <c r="L6" s="20" t="inlineStr">
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>boittiaux2023eiffel</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>@article{boittiaux2023eiffel,   title={Eiffel Tower: A deep-sea underwater dataset for long-term visual localization},   author={Boittiaux, Cl{\'e}mentin and Dune, Claire and Ferrera, Maxime and Arnaubec, Aur{\'e}lien and Marxer, Ricard and Matabos, Marjolaine and Van Audenhaege, Lo{\"i}c and Hugel, Vincent},   journal={The International Journal of Robotics Research},   volume={42},   number={9},   pages={689--699},   publisher={SAGE Publications Sage UK: London, England},   year={2023} }</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M6" s="20" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N6" s="20" t="inlineStr">
+      <c r="O6" s="21" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O6" s="20" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="20" t="inlineStr"/>
-      <c r="R6" s="20" t="inlineStr">
+      <c r="Q6" s="21" t="inlineStr"/>
+      <c r="R6" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S6" s="21" t="inlineStr">
         <is>
           <t>CC-BY-NC-ND-4.0</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>eth</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>ETH3D SLAM &amp; Stereo Benchmarks</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>📸🏠🤳</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>mono, rgbd</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>https://www.eth3d.net/</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr"/>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>BAD SLAM: Bundle Adjusted Direct RGB-D SLAM</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>https://openaccess.thecvf.com/content_CVPR_2019/papers/Schops_BAD_SLAM_Bundle_Adjusted_Direct_RGB-D_SLAM_CVPR_2019_paper.pdf</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J7" s="24" t="inlineStr">
         <is>
           <t>Thomas Schöps, Johannes L. Schönberger, Others</t>
         </is>
       </c>
-      <c r="J7" s="23" t="inlineStr"/>
-      <c r="K7" s="23" t="inlineStr"/>
-      <c r="L7" s="23" t="inlineStr">
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>schops2019bad</t>
+        </is>
+      </c>
+      <c r="L7" s="24" t="inlineStr">
+        <is>
+          <t>@inproceedings{schops2019bad,   title={Bad slam: Bundle adjusted direct rgb-d slam},   author={Schops, Thomas and Sattler, Torsten and Pollefeys, Marc},   booktitle={Proceedings of the IEEE/CVF Conference on Computer Vision and Pattern Recognition},   pages={134--144},   year={2019} }</t>
+        </is>
+      </c>
+      <c r="M7" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr">
+      <c r="N7" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N7" s="23" t="inlineStr">
+      <c r="O7" s="24" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O7" s="23" t="inlineStr">
+      <c r="P7" s="24" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P7" s="23" t="inlineStr"/>
-      <c r="Q7" s="23" t="inlineStr"/>
-      <c r="R7" s="23" t="inlineStr">
+      <c r="Q7" s="24" t="inlineStr"/>
+      <c r="R7" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S7" s="24" t="inlineStr">
         <is>
           <t>CC BY-NC-SA 4.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>euroc</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>EuRoC MAV visual-inertial dataset with stereo images, IMU, and ground-truth trajectories from a micro aerial vehicle</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>📸🏞️🚁</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>radtan4</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>https://projects.asl.ethz.ch/datasets/euroc-mav/</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr"/>
-      <c r="H8" s="20" t="inlineStr"/>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>The EuRoC micro aerial vehicle datasets</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>https://journals.sagepub.com/doi/full/10.1177/0278364915620033</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t>Michael Burri, Janosch Nikolic, Pascal Gohl, Thomas Schneider, Joern Rehder, Sammy Omari, Markus W. Achtelik, Roland Siegwart</t>
         </is>
       </c>
-      <c r="J8" s="20" t="inlineStr"/>
-      <c r="K8" s="20" t="inlineStr"/>
-      <c r="L8" s="20" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>burri2016euroc</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>@article{burri2016euroc,   title={The EuRoC micro aerial vehicle datasets},   author={Burri, Michael and Nikolic, Janosch and Gohl, Pascal and Schneider, Thomas and Rehder, Joern and Omari, Sammy and Achtelik, Markus W and Siegwart, Roland},   journal={The International Journal of Robotics Research},   volume={35},   number={10},   pages={1157--1163},   year={2016},   publisher={SAGE Publications Sage UK: London, England} }</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M8" s="20" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N8" s="20" t="inlineStr">
+      <c r="O8" s="21" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O8" s="20" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P8" s="20" t="inlineStr">
+      <c r="Q8" s="21" t="inlineStr">
         <is>
           <t>complete_dataset</t>
         </is>
       </c>
-      <c r="Q8" s="20" t="inlineStr"/>
-      <c r="R8" s="20" t="inlineStr">
+      <c r="R8" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S8" s="21" t="inlineStr">
         <is>
           <t>Not explicitly stated (research/academic use)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>hamlyn</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Hamlyn rectified stereo endoscopy dataset with depth ground truth, from Endo-Depth-and-Motion</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>📸🫀🤳</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>mono, rgbd, stereo</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>https://davidrecasens.github.io/EndoDepthAndMotion/</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr"/>
-      <c r="H9" s="23" t="inlineStr"/>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Endo-Depth-and-Motion: Reconstruction and Tracking in Endoscopic Videos Using Depth Networks and Photometric Constraints</t>
+        </is>
+      </c>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/abstract/document/9478277</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J9" s="24" t="inlineStr">
         <is>
           <t>David Recasens, José Lamarca, José M. Fácil, J. M. M. Montiel, Javier Civera</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr"/>
-      <c r="K9" s="23" t="inlineStr"/>
-      <c r="L9" s="23" t="inlineStr">
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>recasens2021endo</t>
+        </is>
+      </c>
+      <c r="L9" s="24" t="inlineStr">
+        <is>
+          <t>@article{recasens2021endo,   title={Endo-depth-and-motion: Reconstruction and tracking in endoscopic videos using depth networks and photometric constraints},   author={Recasens, David and Lamarca, Jos{\'e} and F{\'a}cil, Jos{\'e} M and Montiel, JMM and Civera, Javier},   journal={IEEE Robotics and Automation Letters},   volume={6},   number={4},   pages={7225--7232},   year={2021},   publisher={IEEE} }</t>
+        </is>
+      </c>
+      <c r="M9" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M9" s="23" t="inlineStr">
+      <c r="N9" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N9" s="23" t="inlineStr">
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O9" s="23" t="inlineStr">
+      <c r="P9" s="24" t="inlineStr">
         <is>
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="P9" s="23" t="inlineStr"/>
-      <c r="Q9" s="23" t="inlineStr"/>
-      <c r="R9" s="23" t="inlineStr">
+      <c r="Q9" s="24" t="inlineStr"/>
+      <c r="R9" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S9" s="24" t="inlineStr">
         <is>
           <t>GPL-3.0 License</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>hilti2022</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Hilti-Oxford SLAM Challenge 2022 - multi-camera, IMU and lidar dataset for SLAM benchmarking in construction and industrial environments</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>📸🏠🏞️🏗️🤳</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>mono, mono-vi, stereo, stereo-vi</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>equid4</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>https://hilti-challenge.com/dataset-2022</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>HILTI-Oxford Dataset: A Millimeter-Accurate Benchmark for Simultaneous Localization and Mapping</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2208.09825</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t>Lintong Zhang, Michael Helmberger, Lanke Frank Tarimo Fu, David Wisth, Marco Camurri, Davide Scaramuzza, Maurice Fallon</t>
         </is>
       </c>
-      <c r="J10" s="20" t="inlineStr"/>
-      <c r="K10" s="20" t="inlineStr"/>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>zhang2022hilti</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>@article{zhang2022hilti,   title={Hilti-oxford dataset: A millimeter-accurate benchmark for simultaneous localization and mapping},   author={Zhang, Lintong and Helmberger, Michael and Fu, Lanke Frank Tarimo and Wisth, David and Camurri, Marco and Scaramuzza, Davide and Fallon, Maurice},   journal={IEEE Robotics and Automation Letters},   volume={8},   number={1},   pages={408--415},   year={2022},   publisher={IEEE} }</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M10" s="20" t="inlineStr">
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N10" s="20" t="inlineStr">
+      <c r="O10" s="21" t="inlineStr">
         <is>
           <t>ros1, zip</t>
         </is>
       </c>
-      <c r="O10" s="20" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P10" s="20" t="inlineStr"/>
-      <c r="Q10" s="20" t="inlineStr"/>
-      <c r="R10" s="20" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr"/>
+      <c r="R10" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S10" s="21" t="inlineStr">
         <is>
           <t>CC BY-NC-SA 3.0</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>hilti2026</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Hilti x Trimble 360 Visual-Inertial SLAM Challenge 2026 - construction-site benchmark with floor plan priors, captured with a dual-fisheye 360 camera and LiDAR-based ground truth</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>📸🏠🏞️🏗️🤳</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>mono, mono-vi</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>equid4</t>
         </is>
       </c>
-      <c r="F11" s="24" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>https://github.com/Hilti-Research/hilti-trimble-slam-challenge-2026</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr"/>
-      <c r="H11" s="23" t="inlineStr"/>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Hilti-Trimble-Oxford Dataset: 360 Visual-Inertial Benchmark with Floor Plan Priors for SLAM and Localization</t>
+        </is>
+      </c>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2607.06464</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J11" s="24" t="inlineStr">
         <is>
           <t>Samuele Centanni, Yuhao Zhang, Yifu Tao, Julien Kindle, Frank Neuhaus, Tilman Koß, Aryaman Patel, Michael Helmberger, Emilia Szymańska, Torben Gräber, Maurice Fallon</t>
         </is>
       </c>
-      <c r="J11" s="23" t="inlineStr"/>
-      <c r="K11" s="23" t="inlineStr"/>
-      <c r="L11" s="23" t="inlineStr">
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>slamchallenge2026</t>
+        </is>
+      </c>
+      <c r="L11" s="24" t="inlineStr">
+        <is>
+          <t>@misc{slamchallenge2026,   title={{Hilti}-{Trimble}-{Oxford} Dataset: 360 Visual-Inertial Benchmark with Floor Plan Priors for SLAM and Localization},   author={Centanni, Samuele and Zhang, Yuhao and Tao, Yifu and Kindle, Julien and Neuhaus, Frank and Ko{\ss}, Tilman and Patel, Aryaman and Helmberger, Michael and Szyma{\'n}ska, Emilia and Gr{\"a}ber, Torben and Fallon, Maurice},   eprint={2607.06464},   url={https://arxiv.org/abs/2607.06464},   year={2026} }</t>
+        </is>
+      </c>
+      <c r="M11" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M11" s="23" t="inlineStr">
+      <c r="N11" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N11" s="23" t="inlineStr">
+      <c r="O11" s="24" t="inlineStr">
         <is>
           <t>ros2</t>
         </is>
       </c>
-      <c r="O11" s="23" t="inlineStr">
+      <c r="P11" s="24" t="inlineStr">
         <is>
           <t>google-drive</t>
         </is>
       </c>
-      <c r="P11" s="23" t="inlineStr"/>
-      <c r="Q11" s="23" t="inlineStr"/>
-      <c r="R11" s="23" t="inlineStr">
+      <c r="Q11" s="24" t="inlineStr"/>
+      <c r="R11" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S11" s="24" t="inlineStr">
         <is>
           <t>CC BY-NC-SA 3.0</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>kitti</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>KITTI Odometry Benchmark with stereo image sequences and ground-truth poses for visual odometry/SLAM</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>📸🏞️🚗</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>mono, stereo</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>https://www.cvlibs.net/datasets/kitti/</t>
         </is>
       </c>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>Are We Ready for Autonomous Driving? The KITTI Vision Benchmark Suite</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/abstract/document/6248074</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t>Andreas Geiger, Philip Lenz, Christoph Stiller, Raquel Urtasun</t>
         </is>
       </c>
-      <c r="J12" s="20" t="inlineStr"/>
-      <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr">
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>geiger2012we</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>@inproceedings{geiger2012we,   title={Are we ready for autonomous driving? the kitti vision benchmark suite},   author={Geiger, Andreas and Lenz, Philip and Urtasun, Raquel},   booktitle={2012 IEEE conference on computer vision and pattern recognition},   pages={3354--3361},   year={2012},   organization={IEEE} }</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M12" s="20" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N12" s="20" t="inlineStr">
+      <c r="O12" s="21" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P12" s="20" t="inlineStr">
+      <c r="Q12" s="21" t="inlineStr">
         <is>
           <t>complete_dataset</t>
         </is>
       </c>
-      <c r="Q12" s="20" t="inlineStr"/>
-      <c r="R12" s="20" t="inlineStr">
+      <c r="R12" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S12" s="21" t="inlineStr">
         <is>
           <t>CC BY-NC-SA 3.0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>madmax</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>The MADMAX data set for visual-inertial rover navigation on Mars</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>📸🏞️🪐🤳</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>mono, mono-vi, stereo, stereo-vi</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>https://datasets.arches-projekt.de/morocco2018/</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr"/>
-      <c r="H13" s="23" t="inlineStr"/>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>The MADMAX data set for visual-inertial rover navigation on Mars</t>
+        </is>
+      </c>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/rob.22016</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="J13" s="24" t="inlineStr">
         <is>
           <t>Lukas Meyer, Michal Smíšek, Others</t>
         </is>
       </c>
-      <c r="J13" s="23" t="inlineStr"/>
-      <c r="K13" s="23" t="inlineStr"/>
-      <c r="L13" s="23" t="inlineStr">
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>meyer2021madmax</t>
+        </is>
+      </c>
+      <c r="L13" s="24" t="inlineStr">
+        <is>
+          <t>@article{meyer2021madmax,   title={The MADMAX data set for visual-inertial rover navigation on Mars},   author={Meyer, Lukas and Smisek, Michal and Fontan Villacampa, Alejandro and Oliva Maza, Laura and Medina, Daniel and Schuster, Martin J and Steidle, Florian and Vayugundla, Mallikarjuna and M{\"u}ller, Marcus G and Rebele, Bernhard and Wedler, Armin and Triebel, Rudolph},   journal={Journal of Field Robotics},   volume={38},   number={6},   pages={833--853},   publisher={Wiley Online Library},   year={2021} }</t>
+        </is>
+      </c>
+      <c r="M13" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M13" s="23" t="inlineStr">
+      <c r="N13" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N13" s="23" t="inlineStr">
+      <c r="O13" s="24" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O13" s="23" t="inlineStr">
+      <c r="P13" s="24" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P13" s="23" t="inlineStr">
+      <c r="Q13" s="24" t="inlineStr">
         <is>
           <t>api_token</t>
         </is>
       </c>
-      <c r="Q13" s="23" t="inlineStr"/>
-      <c r="R13" s="23" t="inlineStr">
+      <c r="R13" s="24" t="inlineStr">
+        <is>
+          <t>Registration Required</t>
+        </is>
+      </c>
+      <c r="S13" s="24" t="inlineStr">
         <is>
           <t>Academic use only (registration required)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>monotum</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>Photometrically calibrated monocular visual odometry benchmark with 50 real-world sequences, evaluated via accumulated loop-closure drift</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>📸🏠🏞️🤳</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>mono</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>https://cvg.cit.tum.de/data/datasets/mono-dataset</t>
         </is>
       </c>
-      <c r="G14" s="20" t="inlineStr"/>
-      <c r="H14" s="20" t="inlineStr"/>
-      <c r="I14" s="20" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>A Photometrically Calibrated Benchmark for Monocular Visual Odometry</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/1607.02555</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t>Jakob Engel, Vladyslav Usenko, Daniel Cremers</t>
         </is>
       </c>
-      <c r="J14" s="20" t="inlineStr"/>
-      <c r="K14" s="20" t="inlineStr"/>
-      <c r="L14" s="20" t="inlineStr">
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>engel2016photometrically</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>@article{engel2016photometrically,   title={A photometrically calibrated benchmark for monocular visual odometry},   author={Engel, Jakob and Usenko, Vladyslav and Cremers, Daniel},   journal={arXiv preprint arXiv:1607.02555},   year={2016} }</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M14" s="20" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N14" s="20" t="inlineStr">
+      <c r="O14" s="21" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O14" s="20" t="inlineStr">
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P14" s="20" t="inlineStr"/>
-      <c r="Q14" s="20" t="inlineStr"/>
-      <c r="R14" s="20" t="inlineStr">
+      <c r="Q14" s="21" t="inlineStr"/>
+      <c r="R14" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S14" s="21" t="inlineStr">
         <is>
           <t>CC-BY-4.0</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>msd</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Monado SLAM Dataset - Valve Index</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>📸🏠🥽</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>equid4</t>
         </is>
       </c>
-      <c r="F15" s="24" t="inlineStr">
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>https://huggingface.co/datasets/collabora/monado-slam-datasets</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr"/>
-      <c r="H15" s="23" t="inlineStr"/>
-      <c r="I15" s="23" t="inlineStr">
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>The Monado SLAM Dataset for Egocentric Visual-Inertial Tracking</t>
+        </is>
+      </c>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2508.00088</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="inlineStr">
         <is>
           <t>Mateo de Mayo, Daniel Cremers, Taihú Pire</t>
         </is>
       </c>
-      <c r="J15" s="23" t="inlineStr"/>
-      <c r="K15" s="23" t="inlineStr"/>
-      <c r="L15" s="23" t="inlineStr">
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>deMayoCremersPireMSD</t>
+        </is>
+      </c>
+      <c r="L15" s="24" t="inlineStr">
+        <is>
+          <t>@inproceedings{deMayoCremersPireMSD,   title={The Monado SLAM Dataset for Egocentric Visual-Inertial Tracking},   author={{de Mayo}, Mateo and Cremers, Daniel and Pire, Taih{\'u}},   booktitle={2025 IEEE/RSJ International Conference on Intelligent Robots and Systems (IROS)},   pages={13111--13118},   doi={10.1109/IROS60139.2025.11247240},   year={2025} }</t>
+        </is>
+      </c>
+      <c r="M15" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M15" s="23" t="inlineStr">
+      <c r="N15" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N15" s="23" t="inlineStr">
+      <c r="O15" s="24" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O15" s="23" t="inlineStr">
+      <c r="P15" s="24" t="inlineStr">
         <is>
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="P15" s="23" t="inlineStr"/>
-      <c r="Q15" s="23" t="inlineStr"/>
-      <c r="R15" s="23" t="inlineStr">
+      <c r="Q15" s="24" t="inlineStr"/>
+      <c r="R15" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S15" s="24" t="inlineStr">
         <is>
           <t>CC-BY 4.0</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>nsavp</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>Novel Sensors for Autonomous Vehicle Perception - stereo thermal, event, monochrome and RGB cameras time-synchronized with high-precision navigation ground truth, collected from a Ford Fusion driving repeated ~8km urban routes</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>📸🏞️🚗</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>mono, stereo</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>radtan4</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>https://umautobots.github.io/nsavp</t>
         </is>
       </c>
-      <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="inlineStr"/>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>Dataset and Benchmark: Novel Sensors for Autonomous Vehicle Perception</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>https://journals.sagepub.com/doi/abs/10.1177/02783649241273554</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t>Katherine A. Skinner, Ram Vasudevan, Manikandasriram S. Ramanagopal, Radhika Ravi, Spencer Carmichael, Austin D. Buchan</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr"/>
-      <c r="K16" s="20" t="inlineStr"/>
-      <c r="L16" s="20" t="inlineStr">
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>nsavp_2025</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>@article{nsavp_2025,   title={Dataset and Benchmark: Novel Sensors for Autonomous Vehicle Perception},   author={Carmichael, Spencer and Buchan, Austin and Ramanagopal, Mani and Ravi, Radhika and Vasudevan, Ram and Skinner, Katherine A},   journal={The International Journal of Robotics Research},   volume={44},   number={3},   pages={355--365},   year={2025} }</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M16" s="20" t="inlineStr">
+      <c r="N16" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N16" s="20" t="inlineStr">
+      <c r="O16" s="21" t="inlineStr">
         <is>
           <t>hdf5</t>
         </is>
       </c>
-      <c r="O16" s="20" t="inlineStr">
+      <c r="P16" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P16" s="20" t="inlineStr"/>
-      <c r="Q16" s="20" t="inlineStr"/>
-      <c r="R16" s="20" t="inlineStr">
+      <c r="Q16" s="21" t="inlineStr"/>
+      <c r="R16" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S16" s="21" t="inlineStr">
         <is>
           <t>CC-BY-4.0</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>nuim</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>ICL-NUIM RGB-D benchmark with ground-truth trajectories and 3D models for SLAM/odometry evaluation</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>💻🏠🤳</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>mono, rgbd</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>https://www.doc.ic.ac.uk/~ahanda/VaFRIC/iclnuim.html</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr"/>
-      <c r="H17" s="23" t="inlineStr"/>
-      <c r="I17" s="23" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>A benchmark for RGB-D visual odometry, 3D reconstruction and SLAM</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/abstract/document/6907054</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="inlineStr">
         <is>
           <t>Ankur Handa, Thomas Whelan, John B. McDonald, Andrew J. Davison</t>
         </is>
       </c>
-      <c r="J17" s="23" t="inlineStr"/>
-      <c r="K17" s="23" t="inlineStr"/>
-      <c r="L17" s="23" t="inlineStr">
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>handa2014benchmark</t>
+        </is>
+      </c>
+      <c r="L17" s="24" t="inlineStr">
+        <is>
+          <t>@inproceedings{handa2014benchmark,   title={A benchmark for RGB-D visual odometry, 3D reconstruction and SLAM},   author={Handa, Ankur and Whelan, Thomas and McDonald, John and Davison, Andrew J},   booktitle={2014 IEEE international conference on Robotics and automation (ICRA)},   pages={1524--1531},   year={2014},   organization={IEEE} }</t>
+        </is>
+      </c>
+      <c r="M17" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M17" s="23" t="inlineStr">
+      <c r="N17" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N17" s="23" t="inlineStr">
+      <c r="O17" s="24" t="inlineStr">
         <is>
           <t>tar</t>
         </is>
       </c>
-      <c r="O17" s="23" t="inlineStr">
+      <c r="P17" s="24" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P17" s="23" t="inlineStr"/>
-      <c r="Q17" s="23" t="inlineStr"/>
-      <c r="R17" s="23" t="inlineStr">
+      <c r="Q17" s="24" t="inlineStr"/>
+      <c r="R17" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S17" s="24" t="inlineStr">
         <is>
           <t>CC BY 3.0</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>openloris-d400</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>OpenLORIS-Scene - real-world lifelong SLAM dataset from real robots in real scenes</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>📸🏠🤳</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>mono, rgbd, mono-vi, rgbd-vi</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>https://lifelong-robotic-vision.github.io/dataset/scene.html</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="inlineStr"/>
-      <c r="I18" s="20" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/1911.05603</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t>Xuesong Shi, Others</t>
         </is>
       </c>
-      <c r="J18" s="20" t="inlineStr"/>
-      <c r="K18" s="20" t="inlineStr"/>
-      <c r="L18" s="20" t="inlineStr">
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>shi2020openloris</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>@inproceedings{shi2020openloris,   title={Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM},   author={Shi, Xuesong and Li, Dongjiang and Zhao, Pengpeng and Tian, Qinbin and Tian, Yuxin and Long, Qiwei and Zhu, Chunhao and Song, Jingwei and Qiao, Fei and Song, Le and Guo, Yangquan and Wang, Zhigang and Zhang, Yimin and Qin, Baoxing and Yang, Wei and Wang, Fangshi and Chan, Rosa H M and She, Qi},   booktitle={2020 IEEE International Conference on Robotics and Automation (ICRA)},   pages={3139--3145},   year={2020} }</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M18" s="20" t="inlineStr">
+      <c r="N18" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N18" s="20" t="inlineStr">
+      <c r="O18" s="21" t="inlineStr">
         <is>
           <t>tar, 7z</t>
         </is>
       </c>
-      <c r="O18" s="20" t="inlineStr">
+      <c r="P18" s="21" t="inlineStr">
         <is>
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="P18" s="20" t="inlineStr">
+      <c r="Q18" s="21" t="inlineStr">
         <is>
           <t>huggingface_token</t>
         </is>
       </c>
-      <c r="Q18" s="20" t="inlineStr"/>
-      <c r="R18" s="20" t="inlineStr">
+      <c r="R18" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S18" s="21" t="inlineStr">
         <is>
           <t>CC BY-ND 4.0</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="23" t="inlineStr">
         <is>
           <t>openloris-t265</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>OpenLORIS-Scene - real-world lifelong SLAM dataset from real robots in real scenes</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>📸🏠🤳</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>equid4</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>https://lifelong-robotic-vision.github.io/dataset/scene.html</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr"/>
-      <c r="H19" s="23" t="inlineStr"/>
-      <c r="I19" s="23" t="inlineStr">
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM</t>
+        </is>
+      </c>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/1911.05603</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="inlineStr">
         <is>
           <t>Xuesong Shi, Others</t>
         </is>
       </c>
-      <c r="J19" s="23" t="inlineStr"/>
-      <c r="K19" s="23" t="inlineStr"/>
-      <c r="L19" s="23" t="inlineStr">
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>shi2020openloris</t>
+        </is>
+      </c>
+      <c r="L19" s="24" t="inlineStr">
+        <is>
+          <t>@inproceedings{shi2020openloris,   title={Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM},   author={Shi, Xuesong and Li, Dongjiang and Zhao, Pengpeng and Tian, Qinbin and Tian, Yuxin and Long, Qiwei and Zhu, Chunhao and Song, Jingwei and Qiao, Fei and Song, Le and Guo, Yangquan and Wang, Zhigang and Zhang, Yimin and Qin, Baoxing and Yang, Wei and Wang, Fangshi and Chan, Rosa H M and She, Qi},   booktitle={2020 IEEE International Conference on Robotics and Automation (ICRA)},   pages={3139--3145},   year={2020} }</t>
+        </is>
+      </c>
+      <c r="M19" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M19" s="23" t="inlineStr">
+      <c r="N19" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N19" s="23" t="inlineStr">
+      <c r="O19" s="24" t="inlineStr">
         <is>
           <t>tar, 7z</t>
         </is>
       </c>
-      <c r="O19" s="23" t="inlineStr">
+      <c r="P19" s="24" t="inlineStr">
         <is>
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="P19" s="23" t="inlineStr">
+      <c r="Q19" s="24" t="inlineStr">
         <is>
           <t>huggingface_token</t>
         </is>
       </c>
-      <c r="Q19" s="23" t="inlineStr"/>
-      <c r="R19" s="23" t="inlineStr">
+      <c r="R19" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S19" s="24" t="inlineStr">
         <is>
           <t>CC BY-ND 4.0</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>pamir-rig</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Multi-session visual-inertial SLAM dataset of the Pamir shipwreck (Barbados), captured with action cameras and IMU across three scuba dives</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>📸🌊🤳</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>mono, mono-vi, stereo, stereo-vi</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>https://huggingface.co/datasets/afrl-uw/Pamir_Visual-Inertial_Data</t>
         </is>
       </c>
-      <c r="G20" s="20" t="inlineStr"/>
-      <c r="H20" s="20" t="inlineStr"/>
-      <c r="I20" s="20" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2607.10925</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>Michalis Chatzispyrou, Luke Horgan, Hyunkil Hwang, Harish Sathishchandra, Chinmay Burgul, Monika Roznere, Alberto Quattrini Li, Philippos Mordohai, Ioannis Rekleitis</t>
         </is>
       </c>
-      <c r="J20" s="20" t="inlineStr"/>
-      <c r="K20" s="20" t="inlineStr"/>
-      <c r="L20" s="20" t="inlineStr">
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>ChatzispyrouICRA2026</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>@InProceedings{ChatzispyrouICRA2026,   author={Chatzispyrou, Michalis and Horgan, Luke and Hwang, Hyunkil and Sathishchandra, Harish and Burgul, Chinmay and Roznere, Monika and {Quattrini Li}, Alberto and Mordohai, Philippos and Rekleitis, Ioannis},   title={{Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck}},   booktitle={IEEE International Conference on Robotics and Automation (ICRA)},   year=2026,   month={Jun.},   address={Vienna, Austria} }</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M20" s="20" t="inlineStr">
+      <c r="N20" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N20" s="20" t="inlineStr">
+      <c r="O20" s="21" t="inlineStr">
         <is>
           <t>ros2</t>
         </is>
       </c>
-      <c r="O20" s="20" t="inlineStr">
+      <c r="P20" s="21" t="inlineStr">
         <is>
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="P20" s="20" t="inlineStr"/>
-      <c r="Q20" s="20" t="inlineStr"/>
-      <c r="R20" s="20" t="inlineStr">
+      <c r="Q20" s="21" t="inlineStr"/>
+      <c r="R20" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S20" s="21" t="inlineStr">
         <is>
           <t>License</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>pamir</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Multi-session visual-inertial SLAM dataset of the Pamir shipwreck (Barbados), captured with action cameras and IMU across three scuba dives</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>📸🌊🤳</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>mono, mono-vi</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F21" s="24" t="inlineStr">
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>https://huggingface.co/datasets/afrl-uw/Pamir_Visual-Inertial_Data</t>
         </is>
       </c>
-      <c r="G21" s="23" t="inlineStr"/>
-      <c r="H21" s="23" t="inlineStr"/>
-      <c r="I21" s="23" t="inlineStr">
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2607.10925</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J21" s="24" t="inlineStr">
         <is>
           <t>Michalis Chatzispyrou, Luke Horgan, Hyunkil Hwang, Harish Sathishchandra, Chinmay Burgul, Monika Roznere, Alberto Quattrini Li, Philippos Mordohai, Ioannis Rekleitis</t>
         </is>
       </c>
-      <c r="J21" s="23" t="inlineStr"/>
-      <c r="K21" s="23" t="inlineStr"/>
-      <c r="L21" s="23" t="inlineStr">
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>ChatzispyrouICRA2026</t>
+        </is>
+      </c>
+      <c r="L21" s="24" t="inlineStr">
+        <is>
+          <t>@InProceedings{ChatzispyrouICRA2026,   author={Chatzispyrou, Michalis and Horgan, Luke and Hwang, Hyunkil and Sathishchandra, Harish and Burgul, Chinmay and Roznere, Monika and {Quattrini Li}, Alberto and Mordohai, Philippos and Rekleitis, Ioannis},   title={{Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck}},   booktitle={IEEE International Conference on Robotics and Automation (ICRA)},   year=2026,   month={Jun.},   address={Vienna, Austria} }</t>
+        </is>
+      </c>
+      <c r="M21" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M21" s="23" t="inlineStr">
+      <c r="N21" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N21" s="23" t="inlineStr">
+      <c r="O21" s="24" t="inlineStr">
         <is>
           <t>ros2</t>
         </is>
       </c>
-      <c r="O21" s="23" t="inlineStr">
+      <c r="P21" s="24" t="inlineStr">
         <is>
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="P21" s="23" t="inlineStr"/>
-      <c r="Q21" s="23" t="inlineStr"/>
-      <c r="R21" s="23" t="inlineStr">
+      <c r="Q21" s="24" t="inlineStr"/>
+      <c r="R21" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S21" s="24" t="inlineStr">
         <is>
           <t>License</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>replica</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>Photorealistic 3D indoor scene reconstructions (Replica), with RGB-D SLAM trajectories rendered by iMAP</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>💻🏠🤳</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>mono, rgbd</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>https://github.com/facebookresearch/Replica-Dataset</t>
         </is>
       </c>
-      <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="20" t="inlineStr"/>
-      <c r="I22" s="20" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>The Replica Dataset: A Digital Replica of Indoor Spaces</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/1906.05797</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>Julian Straub, Thomas Whelan, Others (Replica Dataset), Edgar Sucar, Shikun Liu, Joseph Ortiz, Andrew Davison</t>
         </is>
       </c>
-      <c r="J22" s="20" t="inlineStr"/>
-      <c r="K22" s="20" t="inlineStr"/>
-      <c r="L22" s="20" t="inlineStr">
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>replica19arxiv</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>@article{replica19arxiv,   title =   {The {R}eplica Dataset: A Digital Replica of Indoor Spaces},   author =  {Julian Straub and Thomas Whelan and Lingni Ma and Yufan Chen and Erik Wijmans and Simon Green and Jakob J. Engel and Raul Mur-Artal and Carl Ren and Shobhit Verma and Anton Clarkson and Mingfei Yan and Brian Budge and Yajie Yan and Xiaqing Pan and June Yon and Yuyang Zou and Kimberly Leon and Nigel Carter and Jesus Briales and  Tyler Gillingham and  Elias Mueggler and Luis Pesqueira and Manolis Savva and Dhruv Batra and Hauke M. Strasdat and Renzo De Nardi and Michael Goesele and Steven Lovegrove and Richard Newcombe },   journal = {arXiv preprint arXiv:1906.05797},   year =    {2019} }</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M22" s="20" t="inlineStr">
+      <c r="N22" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N22" s="20" t="inlineStr">
+      <c r="O22" s="21" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O22" s="20" t="inlineStr">
+      <c r="P22" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P22" s="20" t="inlineStr">
+      <c r="Q22" s="21" t="inlineStr">
         <is>
           <t>complete_dataset</t>
         </is>
       </c>
-      <c r="Q22" s="20" t="inlineStr"/>
-      <c r="R22" s="20" t="inlineStr">
+      <c r="R22" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S22" s="21" t="inlineStr">
         <is>
           <t>Replica Dataset Research Terms (non-commercial research use)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="22" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>rgbdtum</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>RGB-D SLAM benchmark with motion-capture ground-truth trajectories</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>📸🏠🤳</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>mono, rgbd</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>radtan5</t>
         </is>
       </c>
-      <c r="F23" s="24" t="inlineStr">
+      <c r="F23" s="25" t="inlineStr">
         <is>
           <t>https://cvg.cit.tum.de/data/datasets/rgbd-dataset</t>
         </is>
       </c>
-      <c r="G23" s="23" t="inlineStr"/>
-      <c r="H23" s="23" t="inlineStr"/>
-      <c r="I23" s="23" t="inlineStr">
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>A benchmark for the evaluation of RGB-D SLAM systems</t>
+        </is>
+      </c>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/abstract/document/6385773</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J23" s="24" t="inlineStr">
         <is>
           <t>Jürgen Sturm, Nikolas Engelhard, Felix Endres, Wolfram Burgard, Daniel Cremers</t>
         </is>
       </c>
-      <c r="J23" s="23" t="inlineStr"/>
-      <c r="K23" s="23" t="inlineStr"/>
-      <c r="L23" s="23" t="inlineStr">
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>sturm2012benchmark</t>
+        </is>
+      </c>
+      <c r="L23" s="24" t="inlineStr">
+        <is>
+          <t>@inproceedings{sturm2012benchmark,   title={A benchmark for the evaluation of RGB-D SLAM systems},   author={Sturm, J{\"u}rgen and Engelhard, Nikolas and Endres, Felix and Burgard, Wolfram and Cremers, Daniel},   booktitle={2012 IEEE/RSJ international conference on intelligent robots and systems},   pages={573--580},   year={2012},   organization={IEEE} }</t>
+        </is>
+      </c>
+      <c r="M23" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M23" s="23" t="inlineStr">
+      <c r="N23" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N23" s="23" t="inlineStr">
+      <c r="O23" s="24" t="inlineStr">
         <is>
           <t>tar</t>
         </is>
       </c>
-      <c r="O23" s="23" t="inlineStr">
+      <c r="P23" s="24" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P23" s="23" t="inlineStr"/>
-      <c r="Q23" s="23" t="inlineStr"/>
-      <c r="R23" s="23" t="inlineStr">
+      <c r="Q23" s="24" t="inlineStr"/>
+      <c r="R23" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S23" s="24" t="inlineStr">
         <is>
           <t>CC BY 4.0</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>rover-d435i</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>📸🏞️🤖</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>mono, rgbd, rgbd-vi</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>radtan4</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>https://iis-esslingen.github.io/rover/</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr"/>
-      <c r="H24" s="20" t="inlineStr"/>
-      <c r="I24" s="20" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.02506</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>Fabian Schmidt, Others</t>
         </is>
       </c>
-      <c r="J24" s="20" t="inlineStr"/>
-      <c r="K24" s="20" t="inlineStr"/>
-      <c r="L24" s="20" t="inlineStr">
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>schmidt2025rover</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>@article{schmidt2025rover,   title={ROVER: A Multiseason Dataset for Visual SLAM},   author={Schmidt, Fabian and Daubermann, Julian and Mitschke, Marcel and Blessing, Constantin and Meyer, Stephan and Enzweiler, Markus and Valada, Abhinav},   journal={IEEE Transactions on Robotics},   volume={41},   pages={4005--4022},   year={2025} }</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M24" s="20" t="inlineStr">
+      <c r="N24" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N24" s="20" t="inlineStr">
+      <c r="O24" s="21" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O24" s="20" t="inlineStr">
+      <c r="P24" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P24" s="20" t="inlineStr"/>
-      <c r="Q24" s="20" t="inlineStr"/>
-      <c r="R24" s="20" t="inlineStr">
+      <c r="Q24" s="21" t="inlineStr"/>
+      <c r="R24" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S24" s="21" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>rover-picam</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>📸🏞️🤖</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>mono</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="24" t="inlineStr">
         <is>
           <t>equid4</t>
         </is>
       </c>
-      <c r="F25" s="24" t="inlineStr">
+      <c r="F25" s="25" t="inlineStr">
         <is>
           <t>https://iis-esslingen.github.io/rover/</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr"/>
-      <c r="H25" s="23" t="inlineStr"/>
-      <c r="I25" s="23" t="inlineStr">
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
+        </is>
+      </c>
+      <c r="H25" s="25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.02506</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J25" s="24" t="inlineStr">
         <is>
           <t>Fabian Schmidt, Others</t>
         </is>
       </c>
-      <c r="J25" s="23" t="inlineStr"/>
-      <c r="K25" s="23" t="inlineStr"/>
-      <c r="L25" s="23" t="inlineStr">
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>schmidt2025rover</t>
+        </is>
+      </c>
+      <c r="L25" s="24" t="inlineStr">
+        <is>
+          <t>@article{schmidt2025rover,   title={ROVER: A Multiseason Dataset for Visual SLAM},   author={Schmidt, Fabian and Daubermann, Julian and Mitschke, Marcel and Blessing, Constantin and Meyer, Stephan and Enzweiler, Markus and Valada, Abhinav},   journal={IEEE Transactions on Robotics},   volume={41},   pages={4005--4022},   year={2025} }</t>
+        </is>
+      </c>
+      <c r="M25" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M25" s="23" t="inlineStr">
+      <c r="N25" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N25" s="23" t="inlineStr">
+      <c r="O25" s="24" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O25" s="23" t="inlineStr">
+      <c r="P25" s="24" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P25" s="23" t="inlineStr"/>
-      <c r="Q25" s="23" t="inlineStr"/>
-      <c r="R25" s="23" t="inlineStr">
+      <c r="Q25" s="24" t="inlineStr"/>
+      <c r="R25" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S25" s="24" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>rover-t265</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>📸🏞️🤖</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>equid4</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>https://iis-esslingen.github.io/rover/</t>
         </is>
       </c>
-      <c r="G26" s="20" t="inlineStr"/>
-      <c r="H26" s="20" t="inlineStr"/>
-      <c r="I26" s="20" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2412.02506</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>Fabian Schmidt, Others</t>
         </is>
       </c>
-      <c r="J26" s="20" t="inlineStr"/>
-      <c r="K26" s="20" t="inlineStr"/>
-      <c r="L26" s="20" t="inlineStr">
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>schmidt2025rover</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>@article{schmidt2025rover,   title={ROVER: A Multiseason Dataset for Visual SLAM},   author={Schmidt, Fabian and Daubermann, Julian and Mitschke, Marcel and Blessing, Constantin and Meyer, Stephan and Enzweiler, Markus and Valada, Abhinav},   journal={IEEE Transactions on Robotics},   volume={41},   pages={4005--4022},   year={2025} }</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M26" s="20" t="inlineStr">
+      <c r="N26" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N26" s="20" t="inlineStr">
+      <c r="O26" s="21" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O26" s="20" t="inlineStr">
+      <c r="P26" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P26" s="20" t="inlineStr"/>
-      <c r="Q26" s="20" t="inlineStr"/>
-      <c r="R26" s="20" t="inlineStr">
+      <c r="Q26" s="21" t="inlineStr"/>
+      <c r="R26" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S26" s="21" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>s3li_etna</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>S3LI Etna - the DLR Planetary Stereo, Solid-State LiDAR, Inertial dataset, recorded on the moon-like volcanic slopes of Mt. Etna, Sicily, for SLAM benchmarking in extremely unstructured environments</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>📸🏞️🪐🤳</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="24" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F27" s="24" t="inlineStr">
+      <c r="F27" s="25" t="inlineStr">
         <is>
           <t>https://www.dlr.de/en/rm/research/publications-and-downloads/datasets/s3li-datasets</t>
         </is>
       </c>
-      <c r="G27" s="23" t="inlineStr"/>
-      <c r="H27" s="23" t="inlineStr"/>
-      <c r="I27" s="23" t="inlineStr">
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Challenges of SLAM in extremely unstructured environments: the DLR Planetary Stereo, Solid-State LiDAR, Inertial Dataset</t>
+        </is>
+      </c>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/LRA.2022.3188118</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J27" s="24" t="inlineStr">
         <is>
           <t>Riccardo Giubilato, Wolfgang Stürzl, Armin Wedler, Rudolph Triebel</t>
         </is>
       </c>
-      <c r="J27" s="23" t="inlineStr"/>
-      <c r="K27" s="23" t="inlineStr"/>
-      <c r="L27" s="23" t="inlineStr">
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>giubilato2022challenges</t>
+        </is>
+      </c>
+      <c r="L27" s="24" t="inlineStr">
+        <is>
+          <t>@article{giubilato2022challenges,   title={Challenges of SLAM in extremely unstructured environments: the DLR Planetary Stereo, Solid-State LiDAR, Inertial Dataset},   author={Giubilato, Riccardo and St{\"u}rzl, Wolfgang and Wedler, Armin and Triebel, Rudolph},   journal={IEEE Robotics and Automation Letters},   volume={7},   number={4},   pages={8721--8728},   publisher={IEEE},   year={2022} }</t>
+        </is>
+      </c>
+      <c r="M27" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M27" s="23" t="inlineStr">
+      <c r="N27" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N27" s="23" t="inlineStr">
+      <c r="O27" s="24" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O27" s="23" t="inlineStr">
+      <c r="P27" s="24" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P27" s="23" t="inlineStr"/>
-      <c r="Q27" s="23" t="inlineStr"/>
-      <c r="R27" s="23" t="inlineStr">
+      <c r="Q27" s="24" t="inlineStr"/>
+      <c r="R27" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S27" s="24" t="inlineStr">
         <is>
           <t>Not explicitly stated by DLR (research/academic use)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>s3li_vulcano</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>S3LI Vulcano - a multi-modal (RGB stereo, solid-state LiDAR, inertial) dataset for SLAM and place recognition in unstructured planetary-analogue environments, recorded on the volcanic island of Vulcano, Sicily</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>📸🏞️🪐🤳</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>https://www.dlr.de/en/rm/research/publications-and-downloads/datasets/s3li-datasets</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="20" t="inlineStr"/>
-      <c r="I28" s="20" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>The S3LI Vulcano Dataset: A Dataset for Multi-Modal SLAM in Unstructured Planetary Environments</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2601.19557</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>Riccardo Giubilato, Marcus Gerhard Müller, Marco Sewtz, Laura Alejandra Encinar Gonzalez, John Folkesson, Rudolph Triebel</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr"/>
-      <c r="K28" s="20" t="inlineStr"/>
-      <c r="L28" s="20" t="inlineStr">
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>giubilato2026s3livulcano</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>@misc{giubilato2026s3livulcano,   title={The S3LI Vulcano Dataset: A Dataset for Multi-Modal SLAM in Unstructured Planetary Environments},   author={Giubilato, Riccardo and M{\"u}ller, Marcus Gerhard and Sewtz, Marco and Encinar Gonzalez, Laura Alejandra and Folkesson, John and Triebel, Rudolph},   eprint={2601.19557},   archivePrefix={arXiv},   year={2026} }</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M28" s="20" t="inlineStr">
+      <c r="N28" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N28" s="20" t="inlineStr">
+      <c r="O28" s="21" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O28" s="20" t="inlineStr">
+      <c r="P28" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P28" s="20" t="inlineStr"/>
-      <c r="Q28" s="20" t="inlineStr"/>
-      <c r="R28" s="20" t="inlineStr">
+      <c r="Q28" s="21" t="inlineStr"/>
+      <c r="R28" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S28" s="21" t="inlineStr">
         <is>
           <t>Not explicitly stated by DLR (research/academic use)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>sesoko</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>AUV (TUNA-SAND) coral-reef mapping surveys off Sesoko Island, Okinawa, Japan (2016-2018 campaigns), served via the SQUIDLE+ marine imagery platform</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>📸🏞️🌊</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>mono</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="F29" s="24" t="inlineStr">
+      <c r="F29" s="25" t="inlineStr">
         <is>
           <t>https://squidle.org/</t>
         </is>
       </c>
-      <c r="G29" s="23" t="inlineStr"/>
-      <c r="H29" s="23" t="inlineStr"/>
-      <c r="I29" s="23" t="inlineStr">
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J29" s="24" t="inlineStr">
         <is>
           <t>Blair Thornton, Toshihiro Maki, Saki Harii, Oscar Pizarro, Kazuo Nishida</t>
         </is>
       </c>
-      <c r="J29" s="23" t="inlineStr"/>
-      <c r="K29" s="23" t="inlineStr"/>
-      <c r="L29" s="23" t="inlineStr">
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L29" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M29" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M29" s="23" t="inlineStr">
+      <c r="N29" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N29" s="23" t="inlineStr">
+      <c r="O29" s="24" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="O29" s="23" t="inlineStr">
-        <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="P29" s="23" t="inlineStr">
+      <c r="P29" s="24" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="Q29" s="24" t="inlineStr">
         <is>
           <t>api_token</t>
         </is>
       </c>
-      <c r="Q29" s="23" t="inlineStr"/>
-      <c r="R29" s="23" t="inlineStr">
+      <c r="R29" s="24" t="inlineStr">
+        <is>
+          <t>Registration Required</t>
+        </is>
+      </c>
+      <c r="S29" s="24" t="inlineStr">
         <is>
           <t>No explicit license stated by SQUIDLE+ or the source surveys; imagery served via the SQUIDLE+ platform (squidle.org)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>soneva</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>Coral reef time-series photogrammetry (Maldives), from Soneva Conservation and Sustainability Maldives and Wildflow</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>📸🏞️🌊🤳</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>mono</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F30" s="22" t="inlineStr">
         <is>
           <t>https://huggingface.co/datasets/wildflow/soneva-corals</t>
         </is>
       </c>
-      <c r="G30" s="20" t="inlineStr"/>
-      <c r="H30" s="20" t="inlineStr"/>
-      <c r="I30" s="20" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
         <is>
           <t>Ben Yuen, Ayla Kroon, Tom Freer, Ashley Wallis, Johanna Leonhardt, Wildflow</t>
         </is>
       </c>
-      <c r="J30" s="20" t="inlineStr"/>
-      <c r="K30" s="20" t="inlineStr"/>
-      <c r="L30" s="20" t="inlineStr">
+      <c r="K30" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L30" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M30" s="20" t="inlineStr">
+      <c r="N30" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N30" s="20" t="inlineStr">
+      <c r="O30" s="21" t="inlineStr">
         <is>
           <t>images, colmap</t>
         </is>
       </c>
-      <c r="O30" s="20" t="inlineStr">
+      <c r="P30" s="21" t="inlineStr">
         <is>
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="P30" s="20" t="inlineStr">
+      <c r="Q30" s="21" t="inlineStr">
         <is>
           <t>huggingface_token</t>
         </is>
       </c>
-      <c r="Q30" s="20" t="inlineStr"/>
-      <c r="R30" s="20" t="inlineStr">
+      <c r="R30" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S30" s="21" t="inlineStr">
         <is>
           <t>CC-BY-4.0</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>strayscanner</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>An app for collecting raw RGB-D scans on iOS devices.</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>📸🤳</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>mono, rgbd</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="24" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F31" s="24" t="inlineStr">
+      <c r="F31" s="25" t="inlineStr">
         <is>
           <t>https://docs.strayrobots.io/</t>
         </is>
       </c>
-      <c r="G31" s="23" t="inlineStr"/>
-      <c r="H31" s="23" t="inlineStr"/>
-      <c r="I31" s="23" t="inlineStr">
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="24" t="inlineStr">
         <is>
           <t>Kenneth Blomqvist, Martin Smith, Sihat Afnan</t>
         </is>
       </c>
-      <c r="J31" s="23" t="inlineStr"/>
-      <c r="K31" s="23" t="inlineStr"/>
-      <c r="L31" s="23" t="inlineStr">
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="24" t="inlineStr">
         <is>
           <t>Nicolas Marticorena</t>
         </is>
       </c>
-      <c r="M31" s="23" t="inlineStr"/>
-      <c r="N31" s="23" t="inlineStr">
+      <c r="N31" s="24" t="inlineStr"/>
+      <c r="O31" s="24" t="inlineStr">
         <is>
           <t>zip, video, local</t>
         </is>
       </c>
-      <c r="O31" s="23" t="inlineStr">
+      <c r="P31" s="24" t="inlineStr">
         <is>
           <t>hugging-face, local</t>
         </is>
       </c>
-      <c r="P31" s="23" t="inlineStr"/>
-      <c r="Q31" s="23" t="inlineStr"/>
-      <c r="R31" s="23" t="inlineStr">
+      <c r="Q31" s="24" t="inlineStr"/>
+      <c r="R31" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S31" s="24" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>sweetcorals</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>Coral reef 3D photogrammetry (Indonesia), from Wildflow</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>📸🏞️🌊🤳</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>mono</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>pinhole, unknown</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>https://huggingface.co/datasets/wildflow/sweet-corals</t>
         </is>
       </c>
-      <c r="G32" s="20" t="inlineStr"/>
-      <c r="H32" s="20" t="inlineStr"/>
-      <c r="I32" s="20" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="21" t="inlineStr">
         <is>
           <t>Sergei Nozdrenkov, Michael Sweet, University of Derby, BRIN (Indonesia), Coral Spawning Lab, Wildflow, CORDAP</t>
         </is>
       </c>
-      <c r="J32" s="20" t="inlineStr"/>
-      <c r="K32" s="20" t="inlineStr"/>
-      <c r="L32" s="20" t="inlineStr">
+      <c r="K32" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M32" s="20" t="inlineStr">
+      <c r="N32" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N32" s="20" t="inlineStr">
+      <c r="O32" s="21" t="inlineStr">
         <is>
           <t>images, colmap</t>
         </is>
       </c>
-      <c r="O32" s="20" t="inlineStr">
+      <c r="P32" s="21" t="inlineStr">
         <is>
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="P32" s="20" t="inlineStr">
+      <c r="Q32" s="21" t="inlineStr">
         <is>
           <t>huggingface_token</t>
         </is>
       </c>
-      <c r="Q32" s="20" t="inlineStr"/>
-      <c r="R32" s="20" t="inlineStr">
+      <c r="R32" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S32" s="21" t="inlineStr">
         <is>
           <t>CC-BY-4.0</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>tartanair</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>Large-scale photorealistic simulation dataset with multimodal ground truth for SLAM under challenging conditions</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>💻🏞️🤳</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>mono</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E33" s="24" t="inlineStr">
         <is>
           <t>pinhole</t>
         </is>
       </c>
-      <c r="F33" s="24" t="inlineStr">
+      <c r="F33" s="25" t="inlineStr">
         <is>
           <t>https://theairlab.org/tartanair-dataset/</t>
         </is>
       </c>
-      <c r="G33" s="23" t="inlineStr"/>
-      <c r="H33" s="23" t="inlineStr"/>
-      <c r="I33" s="23" t="inlineStr">
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>TartanAir: A Dataset to Push the Limits of Visual SLAM</t>
+        </is>
+      </c>
+      <c r="H33" s="25" t="inlineStr">
+        <is>
+          <t>https://ieeexplore.ieee.org/abstract/document/9341801</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="J33" s="24" t="inlineStr">
         <is>
           <t>Wenshan Wang, Delong Zhu, Xiangwei Wang, Yaoyu Hu, Yuheng Qiu, Chen Wang, Yafei Hu, Ashish Kapoor, Sebastian Scherer</t>
         </is>
       </c>
-      <c r="J33" s="23" t="inlineStr"/>
-      <c r="K33" s="23" t="inlineStr"/>
-      <c r="L33" s="23" t="inlineStr">
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>tartanair2020iros</t>
+        </is>
+      </c>
+      <c r="L33" s="24" t="inlineStr">
+        <is>
+          <t>@article{tartanair2020iros,   title =   {TartanAir: A Dataset to Push the Limits of Visual SLAM},   author =  {Wang, Wenshan and Zhu, Delong and Wang, Xiangwei and Hu, Yaoyu and Qiu, Yuheng and Wang, Chen and Hu, Yafei and Kapoor, Ashish and Scherer, Sebastian},   booktitle = {2020 IEEE/RSJ International Conference on Intelligent Robots and Systems (IROS)},   year =    {2020} }</t>
+        </is>
+      </c>
+      <c r="M33" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M33" s="23" t="inlineStr">
+      <c r="N33" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N33" s="23" t="inlineStr">
+      <c r="O33" s="24" t="inlineStr">
         <is>
           <t>tar, zip</t>
         </is>
       </c>
-      <c r="O33" s="23" t="inlineStr">
+      <c r="P33" s="24" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P33" s="23" t="inlineStr">
+      <c r="Q33" s="24" t="inlineStr">
         <is>
           <t>complete_dataset</t>
         </is>
       </c>
-      <c r="Q33" s="23" t="inlineStr"/>
-      <c r="R33" s="23" t="inlineStr">
+      <c r="R33" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S33" s="24" t="inlineStr">
         <is>
           <t>CC BY 4.0</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>ut-coda</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>The UT Campus Object Dataset (CODa) - egocentric robot perception dataset collected on the UT Austin campus</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>📸🏞️🤖</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>mono, stereo</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>radtan5</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F34" s="22" t="inlineStr">
         <is>
           <t>https://amrl.cs.utexas.edu/coda/</t>
         </is>
       </c>
-      <c r="G34" s="20" t="inlineStr"/>
-      <c r="H34" s="20" t="inlineStr"/>
-      <c r="I34" s="20" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>Toward Robust Robot 3-D Perception in Urban Environments: The UT Campus Object Dataset</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/TRO.2024.3400831</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="J34" s="21" t="inlineStr">
         <is>
           <t>Arthur Zhang, Joydeep Biswas, Others</t>
         </is>
       </c>
-      <c r="J34" s="20" t="inlineStr"/>
-      <c r="K34" s="20" t="inlineStr"/>
-      <c r="L34" s="20" t="inlineStr">
+      <c r="K34" s="21" t="inlineStr">
+        <is>
+          <t>zhang2024coda</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>@article{zhang2024coda,   title={Toward Robust Robot 3-D Perception in Urban Environments: The UT Campus Object Dataset},   author={Zhang, Arthur and Eranki, Chaitanya and Zhang, Christina and Park, Ji-Hwan and Hong, Raymond and Kalyani, Pranav and Kalyanaraman, Lochana and Gamare, Arsh and Bagad, Arnav and Esteva, Maria and Biswas, Joydeep},   journal={IEEE Transactions on Robotics},   volume={40},   publisher={IEEE},   year={2024} }</t>
+        </is>
+      </c>
+      <c r="M34" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M34" s="20" t="inlineStr">
+      <c r="N34" s="21" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N34" s="20" t="inlineStr">
+      <c r="O34" s="21" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O34" s="20" t="inlineStr">
+      <c r="P34" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P34" s="20" t="inlineStr"/>
-      <c r="Q34" s="20" t="inlineStr"/>
-      <c r="R34" s="20" t="inlineStr">
+      <c r="Q34" s="21" t="inlineStr"/>
+      <c r="R34" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S34" s="21" t="inlineStr">
         <is>
           <t>CC BY-NC-SA 4.0</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>vector</t>
         </is>
       </c>
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
         <is>
           <t>VECtor - a versatile event-centric benchmark for multi-sensor SLAM, with a regular stereo camera, an event stereo camera, an RGB-D sensor, a LiDAR and an IMU, covering small-scale (motion-capture ground truth) and large-scale (LiDAR-ICP ground truth) indoor sequences</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>📸🏠🤳🤖</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E35" s="24" t="inlineStr">
         <is>
           <t>radtan4</t>
         </is>
       </c>
-      <c r="F35" s="24" t="inlineStr">
+      <c r="F35" s="25" t="inlineStr">
         <is>
           <t>https://star-datasets.github.io/vector/</t>
         </is>
       </c>
-      <c r="G35" s="23" t="inlineStr"/>
-      <c r="H35" s="23" t="inlineStr"/>
-      <c r="I35" s="23" t="inlineStr">
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>VECtor: A Versatile Event-Centric Benchmark for Multi-Sensor SLAM</t>
+        </is>
+      </c>
+      <c r="H35" s="25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2207.01404</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J35" s="24" t="inlineStr">
         <is>
           <t>Ling Gao, Yuxuan Liang, Jiaqi Yang, Shaoxun Wu, Chenyu Wang, Jiaben Chen, Laurent Kneip</t>
         </is>
       </c>
-      <c r="J35" s="23" t="inlineStr"/>
-      <c r="K35" s="23" t="inlineStr"/>
-      <c r="L35" s="23" t="inlineStr">
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>gao2022vector</t>
+        </is>
+      </c>
+      <c r="L35" s="24" t="inlineStr">
+        <is>
+          <t>@article{gao2022vector,   title={VECtor: A Versatile Event-Centric Benchmark for Multi-Sensor SLAM},   author={Gao, Ling and Liang, Yuxuan and Yang, Jiaqi and Wu, Shaoxun and Wang, Chenyu and Chen, Jiaben and Kneip, Laurent},   journal={IEEE Robotics and Automation Letters},   volume={7},   number={3},   pages={8217--8224},   publisher={IEEE},   year={2022} }</t>
+        </is>
+      </c>
+      <c r="M35" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M35" s="23" t="inlineStr">
+      <c r="N35" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N35" s="23" t="inlineStr">
+      <c r="O35" s="24" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="O35" s="23" t="inlineStr">
+      <c r="P35" s="24" t="inlineStr">
         <is>
           <t>google-drive</t>
         </is>
       </c>
-      <c r="P35" s="23" t="inlineStr"/>
-      <c r="Q35" s="23" t="inlineStr"/>
-      <c r="R35" s="23" t="inlineStr">
+      <c r="Q35" s="24" t="inlineStr"/>
+      <c r="R35" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S35" s="24" t="inlineStr">
         <is>
           <t>BSD-3-Clause Clear License</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>videos</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>Videos recorded for VSLAM-LAB</t>
         </is>
       </c>
-      <c r="C36" s="20" t="inlineStr"/>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr"/>
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>mono</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>unknown, pinhole</t>
         </is>
       </c>
-      <c r="F36" s="21" t="inlineStr">
+      <c r="F36" s="22" t="inlineStr">
         <is>
           <t>https://huggingface.co/datasets/vslamlab/videos</t>
         </is>
       </c>
-      <c r="G36" s="20" t="inlineStr"/>
-      <c r="H36" s="20" t="inlineStr"/>
-      <c r="I36" s="20" t="inlineStr">
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J36" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="J36" s="20" t="inlineStr"/>
-      <c r="K36" s="20" t="inlineStr"/>
-      <c r="L36" s="20" t="inlineStr">
+      <c r="K36" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L36" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M36" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M36" s="20" t="inlineStr">
+      <c r="N36" s="21" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="N36" s="20" t="inlineStr">
+      <c r="O36" s="21" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="O36" s="20" t="inlineStr">
+      <c r="P36" s="21" t="inlineStr">
         <is>
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="P36" s="20" t="inlineStr"/>
-      <c r="Q36" s="20" t="inlineStr"/>
-      <c r="R36" s="20" t="inlineStr">
+      <c r="Q36" s="21" t="inlineStr"/>
+      <c r="R36" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S36" s="21" t="inlineStr">
         <is>
           <t>GPLv3 License</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>vitum</t>
         </is>
       </c>
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="24" t="inlineStr">
         <is>
           <t>TUM Visual-Inertial Dataset - stereo fisheye and IMU sequences from a handheld rig, with motion-capture ground truth, for visual-inertial odometry/SLAM evaluation</t>
         </is>
       </c>
-      <c r="C37" s="23" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>📸🏠🏞️🤳</t>
         </is>
       </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="D37" s="24" t="inlineStr">
         <is>
           <t>mono, mono-vi, stereo, stereo-vi</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E37" s="24" t="inlineStr">
         <is>
           <t>equid4</t>
         </is>
       </c>
-      <c r="F37" s="24" t="inlineStr">
+      <c r="F37" s="25" t="inlineStr">
         <is>
           <t>https://cvg.cit.tum.de/data/datasets/visual-inertial-dataset</t>
         </is>
       </c>
-      <c r="G37" s="23" t="inlineStr"/>
-      <c r="H37" s="23" t="inlineStr"/>
-      <c r="I37" s="23" t="inlineStr">
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>The TUM VI Benchmark for Evaluating Visual-Inertial Odometry</t>
+        </is>
+      </c>
+      <c r="H37" s="25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/1804.06120</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="J37" s="24" t="inlineStr">
         <is>
           <t>David Schubert, Thore Goll, Nikolaus Demmel, Vladyslav Usenko, Jörg Stückler, Daniel Cremers</t>
         </is>
       </c>
-      <c r="J37" s="23" t="inlineStr"/>
-      <c r="K37" s="23" t="inlineStr"/>
-      <c r="L37" s="23" t="inlineStr">
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>schubert2018vidataset</t>
+        </is>
+      </c>
+      <c r="L37" s="24" t="inlineStr">
+        <is>
+          <t>@inproceedings{schubert2018vidataset,   title={The TUM VI Benchmark for Evaluating Visual-Inertial Odometry},   author={Schubert, D. and Goll, T. and Demmel, N. and Usenko, V. and Stueckler, J. and Cremers, D.},   booktitle={International Conference on Intelligent Robots and Systems (IROS)},   year={2018} }</t>
+        </is>
+      </c>
+      <c r="M37" s="24" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M37" s="23" t="inlineStr">
+      <c r="N37" s="24" t="inlineStr">
         <is>
           <t>Claude (Sonnet 5)</t>
         </is>
       </c>
-      <c r="N37" s="23" t="inlineStr">
+      <c r="O37" s="24" t="inlineStr">
         <is>
           <t>tar</t>
         </is>
       </c>
-      <c r="O37" s="23" t="inlineStr">
+      <c r="P37" s="24" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P37" s="23" t="inlineStr"/>
-      <c r="Q37" s="23" t="inlineStr"/>
-      <c r="R37" s="23" t="inlineStr">
+      <c r="Q37" s="24" t="inlineStr"/>
+      <c r="R37" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S37" s="24" t="inlineStr">
         <is>
           <t>CC BY 4.0</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>youtube</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>Youtube videos of VSLAM sequences.</t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr"/>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr"/>
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>mono</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>radtan4, unknown</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>https://youtu.be/kcfs1-ryKWE</t>
         </is>
       </c>
-      <c r="G38" s="20" t="inlineStr"/>
-      <c r="H38" s="20" t="inlineStr"/>
-      <c r="I38" s="20" t="inlineStr">
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J38" s="21" t="inlineStr">
         <is>
           <t>Unknown uploader</t>
         </is>
       </c>
-      <c r="J38" s="20" t="inlineStr"/>
-      <c r="K38" s="20" t="inlineStr"/>
-      <c r="L38" s="20" t="inlineStr">
+      <c r="K38" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L38" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M38" s="21" t="inlineStr">
         <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="M38" s="20" t="inlineStr">
+      <c r="N38" s="21" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="N38" s="20" t="inlineStr">
+      <c r="O38" s="21" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="O38" s="20" t="inlineStr">
+      <c r="P38" s="21" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="P38" s="20" t="inlineStr"/>
-      <c r="Q38" s="20" t="inlineStr"/>
-      <c r="R38" s="20" t="inlineStr">
+      <c r="Q38" s="21" t="inlineStr"/>
+      <c r="R38" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S38" s="21" t="inlineStr">
         <is>
           <t>Standard YouTube License</t>
         </is>
@@ -3296,46 +4237,83 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId38"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId75"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Datasets/extra-files/dataset_table.xlsx
+++ b/Datasets/extra-files/dataset_table.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -328,8 +328,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Datasets" displayName="Datasets" ref="A1:S38" headerRowCount="1">
-  <autoFilter ref="A1:S38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Datasets" displayName="Datasets" ref="A1:S42" headerRowCount="1">
+  <autoFilter ref="A1:S42"/>
   <tableColumns count="19">
     <tableColumn id="1" name="Dataset"/>
     <tableColumn id="2" name="Summary"/>
@@ -644,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -861,42 +861,42 @@
     <row r="3">
       <c r="A3" s="23" t="inlineStr">
         <is>
-          <t>ariel</t>
+          <t>aria-digital-twin</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>Multi-Camera Underwater Visual-Inertial Dataset - a BlueROV2-based platform (Ariel) surveying a Norwegian fjord and an indoor test tank</t>
+          <t>Aria Digital Twin (ADT) - egocentric dataset captured with Meta's Project Aria glasses in real indoor scenes, with photorealistic simulated ground truth for device trajectory, depth, segmentation, and 3D object/human poses</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
         <is>
-          <t>📸🏠🏞️🌊🤖</t>
+          <t>📸🏠🥽</t>
         </is>
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
-          <t>mono, mono-vi, stereo, stereo-vi</t>
+          <t>mono, mono-vi, stereo, stereo-vi, rgbd, rgbd-vi</t>
         </is>
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t>equid4</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datasets/ntnu-arl/underwater-datasets</t>
+          <t>https://www.projectaria.com/datasets/adt/</t>
         </is>
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
-          <t>An Online Self-calibrating Refractive Camera Model with Application to Underwater Odometry</t>
+          <t>Aria Digital Twin: A New Benchmark Dataset for Egocentric 3D Machine Perception</t>
         </is>
       </c>
       <c r="H3" s="25" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2310.16658</t>
+          <t>https://arxiv.org/abs/2306.06362</t>
         </is>
       </c>
       <c r="I3" s="24" t="inlineStr">
@@ -906,17 +906,17 @@
       </c>
       <c r="J3" s="24" t="inlineStr">
         <is>
-          <t>Mohit Singh, Mihir Dharmadhikari, Kostas Alexis</t>
+          <t>Xiaqing Pan, Nicholas Charron, Yongqian Yang, Scott Peters, Thomas Whelan, Chen Kong, Omkar Parkhi, Richard Newcombe, Carl Yuheng Ren</t>
         </is>
       </c>
       <c r="K3" s="24" t="inlineStr">
         <is>
-          <t>singh2023online</t>
+          <t>pan2023aria</t>
         </is>
       </c>
       <c r="L3" s="24" t="inlineStr">
         <is>
-          <t>@misc{singh2023online,       title={An Online Self-calibrating Refractive Camera Model with Application to Underwater Odometry},        author={Mohit Singh and Mihir Dharmadhikari and Kostas Alexis},       year={2023},       eprint={2310.16658},       archivePrefix={arXiv},       primaryClass={cs.RO} }</t>
+          <t>@inproceedings{pan2023aria,   title={Aria Digital Twin: A New Benchmark Dataset for Egocentric 3D Machine Perception},   author={Pan, Xiaqing and Charron, Nicholas and Yang, Yongqian and Peters, Scott and Whelan, Thomas and Kong, Chen and Parkhi, Omkar and Newcombe, Richard and Ren, Carl Yuheng},   booktitle={Proceedings of the IEEE/CVF International Conference on Computer Vision},   year={2023} }</t>
         </is>
       </c>
       <c r="M3" s="24" t="inlineStr">
@@ -931,85 +931,89 @@
       </c>
       <c r="O3" s="24" t="inlineStr">
         <is>
-          <t>ros1</t>
+          <t>vrs</t>
         </is>
       </c>
       <c r="P3" s="24" t="inlineStr">
         <is>
-          <t>hugging-face</t>
-        </is>
-      </c>
-      <c r="Q3" s="24" t="inlineStr"/>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="Q3" s="24" t="inlineStr">
+        <is>
+          <t>cdn_links_file</t>
+        </is>
+      </c>
       <c r="R3" s="24" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Registration Required</t>
         </is>
       </c>
       <c r="S3" s="24" t="inlineStr">
         <is>
-          <t>BSD-3-Clause</t>
+          <t>Aria Digital Twin Dataset License Agreement (custom, non-commercial research use only, no redistribution)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
-          <t>caves</t>
+          <t>ariel</t>
         </is>
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>Underwater Caves Sonar and Vision Data Set - a diver-guided AUV exploration of an underwater cave complex, with sonar, DVL, dual-IMU and vertically-mounted camera data</t>
+          <t>Multi-Camera Underwater Visual-Inertial Dataset - a BlueROV2-based platform (Ariel) surveying a Norwegian fjord and an indoor test tank</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>📸🏞️🌊</t>
+          <t>📸🏠🏞️🌊🤖</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t>mono</t>
+          <t>mono, mono-vi, stereo, stereo-vi</t>
         </is>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>pinhole</t>
+          <t>equid4</t>
         </is>
       </c>
       <c r="F4" s="22" t="inlineStr">
         <is>
-          <t>https://cirs.udg.edu/caves-dataset/</t>
+          <t>https://huggingface.co/datasets/ntnu-arl/underwater-datasets</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
         <is>
-          <t>Underwater caves sonar data set</t>
+          <t>An Online Self-calibrating Refractive Camera Model with Application to Underwater Odometry</t>
         </is>
       </c>
       <c r="H4" s="22" t="inlineStr">
         <is>
-          <t>https://journals.sagepub.com/doi/10.1177/0278364917732838</t>
+          <t>https://arxiv.org/abs/2310.16658</t>
         </is>
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t>Angelos Mallios, Eduard Vidal, Ricard Campos, Marc Carreras</t>
+          <t>Mohit Singh, Mihir Dharmadhikari, Kostas Alexis</t>
         </is>
       </c>
       <c r="K4" s="21" t="inlineStr">
         <is>
-          <t>mallios2017underwater</t>
+          <t>singh2023online</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t>@article{mallios2017underwater,   title={Underwater caves sonar data set},   author={Mallios, Angelos and Vidal, Eduard and Campos, Ricard and Carreras, Marc},   journal={The International Journal of Robotics Research},   volume={36},   number={12},   pages={1247--1251},   year={2017},   publisher={Sage Publications Sage UK: London, England} }</t>
+          <t>@misc{singh2023online,       title={An Online Self-calibrating Refractive Camera Model with Application to Underwater Odometry},        author={Mohit Singh and Mihir Dharmadhikari and Kostas Alexis},       year={2023},       eprint={2310.16658},       archivePrefix={arXiv},       primaryClass={cs.RO} }</t>
         </is>
       </c>
       <c r="M4" s="21" t="inlineStr">
@@ -1024,12 +1028,12 @@
       </c>
       <c r="O4" s="21" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>ros1</t>
         </is>
       </c>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>hugging-face</t>
         </is>
       </c>
       <c r="Q4" s="21" t="inlineStr"/>
@@ -1040,29 +1044,29 @@
       </c>
       <c r="S4" s="21" t="inlineStr">
         <is>
-          <t>CC BY-NC-SA 4.0</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>drunkards</t>
+          <t>caves</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>The Drunkard's Dataset - synthetic RGB-D exploratory camera trajectories with ground truth in non-rigidly deforming indoor scenes</t>
+          <t>Underwater Caves Sonar and Vision Data Set - a diver-guided AUV exploration of an underwater cave complex, with sonar, DVL, dual-IMU and vertically-mounted camera data</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>💻🏠🤳</t>
+          <t>📸🏞️🌊</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>mono, rgbd</t>
+          <t>mono</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -1072,37 +1076,37 @@
       </c>
       <c r="F5" s="25" t="inlineStr">
         <is>
-          <t>https://davidrecasens.github.io/TheDrunkard'sOdometry/</t>
+          <t>https://cirs.udg.edu/caves-dataset/</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>The Drunkard's Odometry: Estimating Camera Motion in Deforming Scenes</t>
+          <t>Underwater caves sonar data set</t>
         </is>
       </c>
       <c r="H5" s="25" t="inlineStr">
         <is>
-          <t>https://proceedings.neurips.cc/paper_files/paper/2023/hash/98c9b79e9c686aadd4d81e34a7773dd1-Abstract-Datasets_and_Benchmarks.html</t>
+          <t>https://journals.sagepub.com/doi/10.1177/0278364917732838</t>
         </is>
       </c>
       <c r="I5" s="24" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="J5" s="24" t="inlineStr">
         <is>
-          <t>David Recasens, Martin R. Oswald, Marc Pollefeys, Javier Civera</t>
+          <t>Angelos Mallios, Eduard Vidal, Ricard Campos, Marc Carreras</t>
         </is>
       </c>
       <c r="K5" s="24" t="inlineStr">
         <is>
-          <t>recasens2024drunkard</t>
+          <t>mallios2017underwater</t>
         </is>
       </c>
       <c r="L5" s="24" t="inlineStr">
         <is>
-          <t>@article{recasens2024drunkard,   title={The Drunkard’s Odometry: Estimating Camera Motion in Deforming Scenes},   author={Recasens Lafuente, David and Oswald, Martin R and Pollefeys, Marc and Civera, Javier},   journal={Advances in Neural Information Processing Systems},   volume={36},   year={2024} }</t>
+          <t>@article{mallios2017underwater,   title={Underwater caves sonar data set},   author={Mallios, Angelos and Vidal, Eduard and Campos, Ricard and Carreras, Marc},   journal={The International Journal of Robotics Research},   volume={36},   number={12},   pages={1247--1251},   year={2017},   publisher={Sage Publications Sage UK: London, England} }</t>
         </is>
       </c>
       <c r="M5" s="24" t="inlineStr">
@@ -1122,7 +1126,7 @@
       </c>
       <c r="P5" s="24" t="inlineStr">
         <is>
-          <t>google-drive</t>
+          <t>website</t>
         </is>
       </c>
       <c r="Q5" s="24" t="inlineStr"/>
@@ -1133,69 +1137,69 @@
       </c>
       <c r="S5" s="24" t="inlineStr">
         <is>
-          <t>MIT License (some components subject to their original licenses)</t>
+          <t>CC BY-NC-SA 4.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>eiffel-tower</t>
+          <t>drunkards</t>
         </is>
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>Deep-sea hydrothermal vent imagery from four ROV Victor6000 survey campaigns (2015-2020) of the Eiffel Tower edifice, with per-campaign COLMAP poses for long-term visual localization</t>
+          <t>The Drunkard's Dataset - synthetic RGB-D exploratory camera trajectories with ground truth in non-rigidly deforming indoor scenes</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>📸🏞️🌊🤖</t>
+          <t>💻🏠🤳</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>mono</t>
+          <t>mono, rgbd</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>radtan4</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>https://www.seanoe.org/data/00810/92226/</t>
+          <t>https://davidrecasens.github.io/TheDrunkard'sOdometry/</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
         <is>
-          <t>Eiffel Tower: A deep-sea underwater dataset for long-term visual localization</t>
+          <t>The Drunkard's Odometry: Estimating Camera Motion in Deforming Scenes</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/02783649231177322</t>
+          <t>https://proceedings.neurips.cc/paper_files/paper/2023/hash/98c9b79e9c686aadd4d81e34a7773dd1-Abstract-Datasets_and_Benchmarks.html</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t>Clémentin Boittiaux, Claire Dune, Maxime Ferrera, Aurélien Arnaubec, Ricard Marxer, Marjolaine Matabos, Loïc Van Audenhaege, Vincent Hugel</t>
+          <t>David Recasens, Martin R. Oswald, Marc Pollefeys, Javier Civera</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
         <is>
-          <t>boittiaux2023eiffel</t>
+          <t>recasens2024drunkard</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t>@article{boittiaux2023eiffel,   title={Eiffel Tower: A deep-sea underwater dataset for long-term visual localization},   author={Boittiaux, Cl{\'e}mentin and Dune, Claire and Ferrera, Maxime and Arnaubec, Aur{\'e}lien and Marxer, Ricard and Matabos, Marjolaine and Van Audenhaege, Lo{\"i}c and Hugel, Vincent},   journal={The International Journal of Robotics Research},   volume={42},   number={9},   pages={689--699},   publisher={SAGE Publications Sage UK: London, England},   year={2023} }</t>
+          <t>@article{recasens2024drunkard,   title={The Drunkard’s Odometry: Estimating Camera Motion in Deforming Scenes},   author={Recasens Lafuente, David and Oswald, Martin R and Pollefeys, Marc and Civera, Javier},   journal={Advances in Neural Information Processing Systems},   volume={36},   year={2024} }</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -1215,7 +1219,7 @@
       </c>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>google-drive</t>
         </is>
       </c>
       <c r="Q6" s="21" t="inlineStr"/>
@@ -1226,69 +1230,69 @@
       </c>
       <c r="S6" s="21" t="inlineStr">
         <is>
-          <t>CC-BY-NC-ND-4.0</t>
+          <t>MIT License (some components subject to their original licenses)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>eth</t>
+          <t>eiffel-tower</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>ETH3D SLAM &amp; Stereo Benchmarks</t>
+          <t>Deep-sea hydrothermal vent imagery from four ROV Victor6000 survey campaigns (2015-2020) of the Eiffel Tower edifice, with per-campaign COLMAP poses for long-term visual localization</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>📸🏠🤳</t>
+          <t>📸🏞️🌊🤖</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>mono, rgbd</t>
+          <t>mono</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>pinhole</t>
+          <t>radtan4</t>
         </is>
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>https://www.eth3d.net/</t>
+          <t>https://www.seanoe.org/data/00810/92226/</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>BAD SLAM: Bundle Adjusted Direct RGB-D SLAM</t>
+          <t>Eiffel Tower: A deep-sea underwater dataset for long-term visual localization</t>
         </is>
       </c>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>https://openaccess.thecvf.com/content_CVPR_2019/papers/Schops_BAD_SLAM_Bundle_Adjusted_Direct_RGB-D_SLAM_CVPR_2019_paper.pdf</t>
+          <t>https://doi.org/10.1177/02783649231177322</t>
         </is>
       </c>
       <c r="I7" s="24" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="J7" s="24" t="inlineStr">
         <is>
-          <t>Thomas Schöps, Johannes L. Schönberger, Others</t>
+          <t>Clémentin Boittiaux, Claire Dune, Maxime Ferrera, Aurélien Arnaubec, Ricard Marxer, Marjolaine Matabos, Loïc Van Audenhaege, Vincent Hugel</t>
         </is>
       </c>
       <c r="K7" s="24" t="inlineStr">
         <is>
-          <t>schops2019bad</t>
+          <t>boittiaux2023eiffel</t>
         </is>
       </c>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>@inproceedings{schops2019bad,   title={Bad slam: Bundle adjusted direct rgb-d slam},   author={Schops, Thomas and Sattler, Torsten and Pollefeys, Marc},   booktitle={Proceedings of the IEEE/CVF Conference on Computer Vision and Pattern Recognition},   pages={134--144},   year={2019} }</t>
+          <t>@article{boittiaux2023eiffel,   title={Eiffel Tower: A deep-sea underwater dataset for long-term visual localization},   author={Boittiaux, Cl{\'e}mentin and Dune, Claire and Ferrera, Maxime and Arnaubec, Aur{\'e}lien and Marxer, Ricard and Matabos, Marjolaine and Van Audenhaege, Lo{\"i}c and Hugel, Vincent},   journal={The International Journal of Robotics Research},   volume={42},   number={9},   pages={689--699},   publisher={SAGE Publications Sage UK: London, England},   year={2023} }</t>
         </is>
       </c>
       <c r="M7" s="24" t="inlineStr">
@@ -1319,69 +1323,69 @@
       </c>
       <c r="S7" s="24" t="inlineStr">
         <is>
-          <t>CC BY-NC-SA 4.0</t>
+          <t>CC-BY-NC-ND-4.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>euroc</t>
+          <t>eth</t>
         </is>
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>EuRoC MAV visual-inertial dataset with stereo images, IMU, and ground-truth trajectories from a micro aerial vehicle</t>
+          <t>ETH3D SLAM &amp; Stereo Benchmarks</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>📸🏞️🚁</t>
+          <t>📸🏠🤳</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>mono, stereo, mono-vi, stereo-vi</t>
+          <t>mono, rgbd</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
         <is>
-          <t>radtan4</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>https://projects.asl.ethz.ch/datasets/euroc-mav/</t>
+          <t>https://www.eth3d.net/</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
         <is>
-          <t>The EuRoC micro aerial vehicle datasets</t>
+          <t>BAD SLAM: Bundle Adjusted Direct RGB-D SLAM</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>https://journals.sagepub.com/doi/full/10.1177/0278364915620033</t>
+          <t>https://openaccess.thecvf.com/content_CVPR_2019/papers/Schops_BAD_SLAM_Bundle_Adjusted_Direct_RGB-D_SLAM_CVPR_2019_paper.pdf</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t>Michael Burri, Janosch Nikolic, Pascal Gohl, Thomas Schneider, Joern Rehder, Sammy Omari, Markus W. Achtelik, Roland Siegwart</t>
+          <t>Thomas Schöps, Johannes L. Schönberger, Others</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
         <is>
-          <t>burri2016euroc</t>
+          <t>schops2019bad</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t>@article{burri2016euroc,   title={The EuRoC micro aerial vehicle datasets},   author={Burri, Michael and Nikolic, Janosch and Gohl, Pascal and Schneider, Thomas and Rehder, Joern and Omari, Sammy and Achtelik, Markus W and Siegwart, Roland},   journal={The International Journal of Robotics Research},   volume={35},   number={10},   pages={1157--1163},   year={2016},   publisher={SAGE Publications Sage UK: London, England} }</t>
+          <t>@inproceedings{schops2019bad,   title={Bad slam: Bundle adjusted direct rgb-d slam},   author={Schops, Thomas and Sattler, Torsten and Pollefeys, Marc},   booktitle={Proceedings of the IEEE/CVF Conference on Computer Vision and Pattern Recognition},   pages={134--144},   year={2019} }</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -1404,11 +1408,7 @@
           <t>website</t>
         </is>
       </c>
-      <c r="Q8" s="21" t="inlineStr">
-        <is>
-          <t>complete_dataset</t>
-        </is>
-      </c>
+      <c r="Q8" s="21" t="inlineStr"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
           <t>Public</t>
@@ -1416,69 +1416,69 @@
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
-          <t>Not explicitly stated (research/academic use)</t>
+          <t>CC BY-NC-SA 4.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>hamlyn</t>
+          <t>euroc</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Hamlyn rectified stereo endoscopy dataset with depth ground truth, from Endo-Depth-and-Motion</t>
+          <t>EuRoC MAV visual-inertial dataset with stereo images, IMU, and ground-truth trajectories from a micro aerial vehicle</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>📸🫀🤳</t>
+          <t>📸🏞️🚁</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>mono, rgbd, stereo</t>
+          <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t>pinhole</t>
+          <t>radtan4</t>
         </is>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>https://davidrecasens.github.io/EndoDepthAndMotion/</t>
+          <t>https://projects.asl.ethz.ch/datasets/euroc-mav/</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>Endo-Depth-and-Motion: Reconstruction and Tracking in Endoscopic Videos Using Depth Networks and Photometric Constraints</t>
+          <t>The EuRoC micro aerial vehicle datasets</t>
         </is>
       </c>
       <c r="H9" s="25" t="inlineStr">
         <is>
-          <t>https://ieeexplore.ieee.org/abstract/document/9478277</t>
+          <t>https://journals.sagepub.com/doi/full/10.1177/0278364915620033</t>
         </is>
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="J9" s="24" t="inlineStr">
         <is>
-          <t>David Recasens, José Lamarca, José M. Fácil, J. M. M. Montiel, Javier Civera</t>
+          <t>Michael Burri, Janosch Nikolic, Pascal Gohl, Thomas Schneider, Joern Rehder, Sammy Omari, Markus W. Achtelik, Roland Siegwart</t>
         </is>
       </c>
       <c r="K9" s="24" t="inlineStr">
         <is>
-          <t>recasens2021endo</t>
+          <t>burri2016euroc</t>
         </is>
       </c>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>@article{recasens2021endo,   title={Endo-depth-and-motion: Reconstruction and tracking in endoscopic videos using depth networks and photometric constraints},   author={Recasens, David and Lamarca, Jos{\'e} and F{\'a}cil, Jos{\'e} M and Montiel, JMM and Civera, Javier},   journal={IEEE Robotics and Automation Letters},   volume={6},   number={4},   pages={7225--7232},   year={2021},   publisher={IEEE} }</t>
+          <t>@article{burri2016euroc,   title={The EuRoC micro aerial vehicle datasets},   author={Burri, Michael and Nikolic, Janosch and Gohl, Pascal and Schneider, Thomas and Rehder, Joern and Omari, Sammy and Achtelik, Markus W and Siegwart, Roland},   journal={The International Journal of Robotics Research},   volume={35},   number={10},   pages={1157--1163},   year={2016},   publisher={SAGE Publications Sage UK: London, England} }</t>
         </is>
       </c>
       <c r="M9" s="24" t="inlineStr">
@@ -1498,10 +1498,14 @@
       </c>
       <c r="P9" s="24" t="inlineStr">
         <is>
-          <t>hugging-face</t>
-        </is>
-      </c>
-      <c r="Q9" s="24" t="inlineStr"/>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="Q9" s="24" t="inlineStr">
+        <is>
+          <t>complete_dataset</t>
+        </is>
+      </c>
       <c r="R9" s="24" t="inlineStr">
         <is>
           <t>Public</t>
@@ -1509,69 +1513,69 @@
       </c>
       <c r="S9" s="24" t="inlineStr">
         <is>
-          <t>GPL-3.0 License</t>
+          <t>Not explicitly stated (research/academic use)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>hilti2022</t>
+          <t>hamlyn</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>Hilti-Oxford SLAM Challenge 2022 - multi-camera, IMU and lidar dataset for SLAM benchmarking in construction and industrial environments</t>
+          <t>Hamlyn rectified stereo endoscopy dataset with depth ground truth, from Endo-Depth-and-Motion</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>📸🏠🏞️🏗️🤳</t>
+          <t>📸🫀🤳</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>mono, mono-vi, stereo, stereo-vi</t>
+          <t>mono, rgbd, stereo</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
         <is>
-          <t>equid4</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>https://hilti-challenge.com/dataset-2022</t>
+          <t>https://davidrecasens.github.io/EndoDepthAndMotion/</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
         <is>
-          <t>HILTI-Oxford Dataset: A Millimeter-Accurate Benchmark for Simultaneous Localization and Mapping</t>
+          <t>Endo-Depth-and-Motion: Reconstruction and Tracking in Endoscopic Videos Using Depth Networks and Photometric Constraints</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2208.09825</t>
+          <t>https://ieeexplore.ieee.org/abstract/document/9478277</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t>Lintong Zhang, Michael Helmberger, Lanke Frank Tarimo Fu, David Wisth, Marco Camurri, Davide Scaramuzza, Maurice Fallon</t>
+          <t>David Recasens, José Lamarca, José M. Fácil, J. M. M. Montiel, Javier Civera</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
         <is>
-          <t>zhang2022hilti</t>
+          <t>recasens2021endo</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t>@article{zhang2022hilti,   title={Hilti-oxford dataset: A millimeter-accurate benchmark for simultaneous localization and mapping},   author={Zhang, Lintong and Helmberger, Michael and Fu, Lanke Frank Tarimo and Wisth, David and Camurri, Marco and Scaramuzza, Davide and Fallon, Maurice},   journal={IEEE Robotics and Automation Letters},   volume={8},   number={1},   pages={408--415},   year={2022},   publisher={IEEE} }</t>
+          <t>@article{recasens2021endo,   title={Endo-depth-and-motion: Reconstruction and tracking in endoscopic videos using depth networks and photometric constraints},   author={Recasens, David and Lamarca, Jos{\'e} and F{\'a}cil, Jos{\'e} M and Montiel, JMM and Civera, Javier},   journal={IEEE Robotics and Automation Letters},   volume={6},   number={4},   pages={7225--7232},   year={2021},   publisher={IEEE} }</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -1586,12 +1590,12 @@
       </c>
       <c r="O10" s="21" t="inlineStr">
         <is>
-          <t>ros1, zip</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>hugging-face</t>
         </is>
       </c>
       <c r="Q10" s="21" t="inlineStr"/>
@@ -1602,19 +1606,19 @@
       </c>
       <c r="S10" s="21" t="inlineStr">
         <is>
-          <t>CC BY-NC-SA 3.0</t>
+          <t>GPL-3.0 License</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>hilti2026</t>
+          <t>hilti2022</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Hilti x Trimble 360 Visual-Inertial SLAM Challenge 2026 - construction-site benchmark with floor plan priors, captured with a dual-fisheye 360 camera and LiDAR-based ground truth</t>
+          <t>Hilti-Oxford SLAM Challenge 2022 - multi-camera, IMU and lidar dataset for SLAM benchmarking in construction and industrial environments</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -1624,7 +1628,7 @@
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>mono, mono-vi</t>
+          <t>mono, mono-vi, stereo, stereo-vi</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -1634,37 +1638,37 @@
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>https://github.com/Hilti-Research/hilti-trimble-slam-challenge-2026</t>
+          <t>https://hilti-challenge.com/dataset-2022</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Hilti-Trimble-Oxford Dataset: 360 Visual-Inertial Benchmark with Floor Plan Priors for SLAM and Localization</t>
+          <t>HILTI-Oxford Dataset: A Millimeter-Accurate Benchmark for Simultaneous Localization and Mapping</t>
         </is>
       </c>
       <c r="H11" s="25" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2607.06464</t>
+          <t>https://arxiv.org/abs/2208.09825</t>
         </is>
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="J11" s="24" t="inlineStr">
         <is>
-          <t>Samuele Centanni, Yuhao Zhang, Yifu Tao, Julien Kindle, Frank Neuhaus, Tilman Koß, Aryaman Patel, Michael Helmberger, Emilia Szymańska, Torben Gräber, Maurice Fallon</t>
+          <t>Lintong Zhang, Michael Helmberger, Lanke Frank Tarimo Fu, David Wisth, Marco Camurri, Davide Scaramuzza, Maurice Fallon</t>
         </is>
       </c>
       <c r="K11" s="24" t="inlineStr">
         <is>
-          <t>slamchallenge2026</t>
+          <t>zhang2022hilti</t>
         </is>
       </c>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>@misc{slamchallenge2026,   title={{Hilti}-{Trimble}-{Oxford} Dataset: 360 Visual-Inertial Benchmark with Floor Plan Priors for SLAM and Localization},   author={Centanni, Samuele and Zhang, Yuhao and Tao, Yifu and Kindle, Julien and Neuhaus, Frank and Ko{\ss}, Tilman and Patel, Aryaman and Helmberger, Michael and Szyma{\'n}ska, Emilia and Gr{\"a}ber, Torben and Fallon, Maurice},   eprint={2607.06464},   url={https://arxiv.org/abs/2607.06464},   year={2026} }</t>
+          <t>@article{zhang2022hilti,   title={Hilti-oxford dataset: A millimeter-accurate benchmark for simultaneous localization and mapping},   author={Zhang, Lintong and Helmberger, Michael and Fu, Lanke Frank Tarimo and Wisth, David and Camurri, Marco and Scaramuzza, Davide and Fallon, Maurice},   journal={IEEE Robotics and Automation Letters},   volume={8},   number={1},   pages={408--415},   year={2022},   publisher={IEEE} }</t>
         </is>
       </c>
       <c r="M11" s="24" t="inlineStr">
@@ -1679,12 +1683,12 @@
       </c>
       <c r="O11" s="24" t="inlineStr">
         <is>
-          <t>ros2</t>
+          <t>ros1, zip</t>
         </is>
       </c>
       <c r="P11" s="24" t="inlineStr">
         <is>
-          <t>google-drive</t>
+          <t>website</t>
         </is>
       </c>
       <c r="Q11" s="24" t="inlineStr"/>
@@ -1702,62 +1706,62 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>kitti</t>
+          <t>hilti2026</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>KITTI Odometry Benchmark with stereo image sequences and ground-truth poses for visual odometry/SLAM</t>
+          <t>Hilti x Trimble 360 Visual-Inertial SLAM Challenge 2026 - construction-site benchmark with floor plan priors, captured with a dual-fisheye 360 camera and LiDAR-based ground truth</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>📸🏞️🚗</t>
+          <t>📸🏠🏞️🏗️🤳</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>mono, stereo</t>
+          <t>mono, mono-vi</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>pinhole</t>
+          <t>equid4</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t>https://www.cvlibs.net/datasets/kitti/</t>
+          <t>https://github.com/Hilti-Research/hilti-trimble-slam-challenge-2026</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
         <is>
-          <t>Are We Ready for Autonomous Driving? The KITTI Vision Benchmark Suite</t>
+          <t>Hilti-Trimble-Oxford Dataset: 360 Visual-Inertial Benchmark with Floor Plan Priors for SLAM and Localization</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
         <is>
-          <t>https://ieeexplore.ieee.org/abstract/document/6248074</t>
+          <t>https://arxiv.org/abs/2607.06464</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t>Andreas Geiger, Philip Lenz, Christoph Stiller, Raquel Urtasun</t>
+          <t>Samuele Centanni, Yuhao Zhang, Yifu Tao, Julien Kindle, Frank Neuhaus, Tilman Koß, Aryaman Patel, Michael Helmberger, Emilia Szymańska, Torben Gräber, Maurice Fallon</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
         <is>
-          <t>geiger2012we</t>
+          <t>slamchallenge2026</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t>@inproceedings{geiger2012we,   title={Are we ready for autonomous driving? the kitti vision benchmark suite},   author={Geiger, Andreas and Lenz, Philip and Urtasun, Raquel},   booktitle={2012 IEEE conference on computer vision and pattern recognition},   pages={3354--3361},   year={2012},   organization={IEEE} }</t>
+          <t>@misc{slamchallenge2026,   title={{Hilti}-{Trimble}-{Oxford} Dataset: 360 Visual-Inertial Benchmark with Floor Plan Priors for SLAM and Localization},   author={Centanni, Samuele and Zhang, Yuhao and Tao, Yifu and Kindle, Julien and Neuhaus, Frank and Ko{\ss}, Tilman and Patel, Aryaman and Helmberger, Michael and Szyma{\'n}ska, Emilia and Gr{\"a}ber, Torben and Fallon, Maurice},   eprint={2607.06464},   url={https://arxiv.org/abs/2607.06464},   year={2026} }</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -1772,19 +1776,15 @@
       </c>
       <c r="O12" s="21" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>ros2</t>
         </is>
       </c>
       <c r="P12" s="21" t="inlineStr">
         <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="Q12" s="21" t="inlineStr">
-        <is>
-          <t>complete_dataset</t>
-        </is>
-      </c>
+          <t>google-drive</t>
+        </is>
+      </c>
+      <c r="Q12" s="21" t="inlineStr"/>
       <c r="R12" s="21" t="inlineStr">
         <is>
           <t>Public</t>
@@ -1799,22 +1799,22 @@
     <row r="13">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>madmax</t>
+          <t>kitti</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>The MADMAX data set for visual-inertial rover navigation on Mars</t>
+          <t>KITTI Odometry Benchmark with stereo image sequences and ground-truth poses for visual odometry/SLAM</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>📸🏞️🪐🤳</t>
+          <t>📸🏞️🚗</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>mono, mono-vi, stereo, stereo-vi</t>
+          <t>mono, stereo</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -1824,37 +1824,37 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>https://datasets.arches-projekt.de/morocco2018/</t>
+          <t>https://www.cvlibs.net/datasets/kitti/</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>The MADMAX data set for visual-inertial rover navigation on Mars</t>
+          <t>Are We Ready for Autonomous Driving? The KITTI Vision Benchmark Suite</t>
         </is>
       </c>
       <c r="H13" s="25" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/rob.22016</t>
+          <t>https://ieeexplore.ieee.org/abstract/document/6248074</t>
         </is>
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="J13" s="24" t="inlineStr">
         <is>
-          <t>Lukas Meyer, Michal Smíšek, Others</t>
+          <t>Andreas Geiger, Philip Lenz, Christoph Stiller, Raquel Urtasun</t>
         </is>
       </c>
       <c r="K13" s="24" t="inlineStr">
         <is>
-          <t>meyer2021madmax</t>
+          <t>geiger2012we</t>
         </is>
       </c>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>@article{meyer2021madmax,   title={The MADMAX data set for visual-inertial rover navigation on Mars},   author={Meyer, Lukas and Smisek, Michal and Fontan Villacampa, Alejandro and Oliva Maza, Laura and Medina, Daniel and Schuster, Martin J and Steidle, Florian and Vayugundla, Mallikarjuna and M{\"u}ller, Marcus G and Rebele, Bernhard and Wedler, Armin and Triebel, Rudolph},   journal={Journal of Field Robotics},   volume={38},   number={6},   pages={833--853},   publisher={Wiley Online Library},   year={2021} }</t>
+          <t>@inproceedings{geiger2012we,   title={Are we ready for autonomous driving? the kitti vision benchmark suite},   author={Geiger, Andreas and Lenz, Philip and Urtasun, Raquel},   booktitle={2012 IEEE conference on computer vision and pattern recognition},   pages={3354--3361},   year={2012},   organization={IEEE} }</t>
         </is>
       </c>
       <c r="M13" s="24" t="inlineStr">
@@ -1879,39 +1879,39 @@
       </c>
       <c r="Q13" s="24" t="inlineStr">
         <is>
-          <t>api_token</t>
+          <t>complete_dataset</t>
         </is>
       </c>
       <c r="R13" s="24" t="inlineStr">
         <is>
-          <t>Registration Required</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="S13" s="24" t="inlineStr">
         <is>
-          <t>Academic use only (registration required)</t>
+          <t>CC BY-NC-SA 3.0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>monotum</t>
+          <t>madmax</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>Photometrically calibrated monocular visual odometry benchmark with 50 real-world sequences, evaluated via accumulated loop-closure drift</t>
+          <t>The MADMAX data set for visual-inertial rover navigation on Mars</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>📸🏠🏞️🤳</t>
+          <t>📸🏞️🪐🤳</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>mono</t>
+          <t>mono, mono-vi, stereo, stereo-vi</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -1921,37 +1921,37 @@
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>https://cvg.cit.tum.de/data/datasets/mono-dataset</t>
+          <t>https://datasets.arches-projekt.de/morocco2018/</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>A Photometrically Calibrated Benchmark for Monocular Visual Odometry</t>
+          <t>The MADMAX data set for visual-inertial rover navigation on Mars</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1607.02555</t>
+          <t>https://doi.org/10.1002/rob.22016</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t>Jakob Engel, Vladyslav Usenko, Daniel Cremers</t>
+          <t>Lukas Meyer, Michal Smíšek, Others</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
         <is>
-          <t>engel2016photometrically</t>
+          <t>meyer2021madmax</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t>@article{engel2016photometrically,   title={A photometrically calibrated benchmark for monocular visual odometry},   author={Engel, Jakob and Usenko, Vladyslav and Cremers, Daniel},   journal={arXiv preprint arXiv:1607.02555},   year={2016} }</t>
+          <t>@article{meyer2021madmax,   title={The MADMAX data set for visual-inertial rover navigation on Mars},   author={Meyer, Lukas and Smisek, Michal and Fontan Villacampa, Alejandro and Oliva Maza, Laura and Medina, Daniel and Schuster, Martin J and Steidle, Florian and Vayugundla, Mallikarjuna and M{\"u}ller, Marcus G and Rebele, Bernhard and Wedler, Armin and Triebel, Rudolph},   journal={Journal of Field Robotics},   volume={38},   number={6},   pages={833--853},   publisher={Wiley Online Library},   year={2021} }</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -1974,77 +1974,81 @@
           <t>website</t>
         </is>
       </c>
-      <c r="Q14" s="21" t="inlineStr"/>
+      <c r="Q14" s="21" t="inlineStr">
+        <is>
+          <t>api_token</t>
+        </is>
+      </c>
       <c r="R14" s="21" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Registration Required</t>
         </is>
       </c>
       <c r="S14" s="21" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>Academic use only (registration required)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>msd</t>
+          <t>malaysia</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Monado SLAM Dataset - Valve Index</t>
+          <t>Handheld underwater coral-reef transect surveys (Malaysia, July 2026 campaign), 1920x1080 RGB at 10 Hz</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>📸🏠🥽</t>
+          <t>📸🏞️🌊🤳</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>mono, stereo, mono-vi, stereo-vi</t>
+          <t>mono</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>equid4</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datasets/collabora/monado-slam-datasets</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>The Monado SLAM Dataset for Egocentric Visual-Inertial Tracking</t>
+          <t>TODO</t>
         </is>
       </c>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2508.00088</t>
+          <t>TODO</t>
         </is>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>TODO</t>
         </is>
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>Mateo de Mayo, Daniel Cremers, Taihú Pire</t>
+          <t>TODO</t>
         </is>
       </c>
       <c r="K15" s="24" t="inlineStr">
         <is>
-          <t>deMayoCremersPireMSD</t>
+          <t>TODO</t>
         </is>
       </c>
       <c r="L15" s="24" t="inlineStr">
         <is>
-          <t>@inproceedings{deMayoCremersPireMSD,   title={The Monado SLAM Dataset for Egocentric Visual-Inertial Tracking},   author={{de Mayo}, Mateo and Cremers, Daniel and Pire, Taih{\'u}},   booktitle={2025 IEEE/RSJ International Conference on Intelligent Robots and Systems (IROS)},   pages={13111--13118},   doi={10.1109/IROS60139.2025.11247240},   year={2025} }</t>
+          <t>TODO</t>
         </is>
       </c>
       <c r="M15" s="24" t="inlineStr">
@@ -2054,90 +2058,90 @@
       </c>
       <c r="N15" s="24" t="inlineStr">
         <is>
-          <t>Claude (Sonnet 5)</t>
+          <t>Claude (Fable 5)</t>
         </is>
       </c>
       <c r="O15" s="24" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>images</t>
         </is>
       </c>
       <c r="P15" s="24" t="inlineStr">
         <is>
-          <t>hugging-face</t>
+          <t>local</t>
         </is>
       </c>
       <c r="Q15" s="24" t="inlineStr"/>
       <c r="R15" s="24" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="S15" s="24" t="inlineStr">
         <is>
-          <t>CC-BY 4.0</t>
+          <t>TODO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>nsavp</t>
+          <t>monotum</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Novel Sensors for Autonomous Vehicle Perception - stereo thermal, event, monochrome and RGB cameras time-synchronized with high-precision navigation ground truth, collected from a Ford Fusion driving repeated ~8km urban routes</t>
+          <t>Photometrically calibrated monocular visual odometry benchmark with 50 real-world sequences, evaluated via accumulated loop-closure drift</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>📸🏞️🚗</t>
+          <t>📸🏠🏞️🤳</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>mono, stereo</t>
+          <t>mono</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>radtan4</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
         <is>
-          <t>https://umautobots.github.io/nsavp</t>
+          <t>https://cvg.cit.tum.de/data/datasets/mono-dataset</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>Dataset and Benchmark: Novel Sensors for Autonomous Vehicle Perception</t>
+          <t>A Photometrically Calibrated Benchmark for Monocular Visual Odometry</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
         <is>
-          <t>https://journals.sagepub.com/doi/abs/10.1177/02783649241273554</t>
+          <t>https://arxiv.org/abs/1607.02555</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
         <is>
-          <t>Katherine A. Skinner, Ram Vasudevan, Manikandasriram S. Ramanagopal, Radhika Ravi, Spencer Carmichael, Austin D. Buchan</t>
+          <t>Jakob Engel, Vladyslav Usenko, Daniel Cremers</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
         <is>
-          <t>nsavp_2025</t>
+          <t>engel2016photometrically</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
         <is>
-          <t>@article{nsavp_2025,   title={Dataset and Benchmark: Novel Sensors for Autonomous Vehicle Perception},   author={Carmichael, Spencer and Buchan, Austin and Ramanagopal, Mani and Ravi, Radhika and Vasudevan, Ram and Skinner, Katherine A},   journal={The International Journal of Robotics Research},   volume={44},   number={3},   pages={355--365},   year={2025} }</t>
+          <t>@article{engel2016photometrically,   title={A photometrically calibrated benchmark for monocular visual odometry},   author={Engel, Jakob and Usenko, Vladyslav and Cremers, Daniel},   journal={arXiv preprint arXiv:1607.02555},   year={2016} }</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -2152,7 +2156,7 @@
       </c>
       <c r="O16" s="21" t="inlineStr">
         <is>
-          <t>hdf5</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="P16" s="21" t="inlineStr">
@@ -2175,62 +2179,62 @@
     <row r="17">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>nuim</t>
+          <t>msd</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>ICL-NUIM RGB-D benchmark with ground-truth trajectories and 3D models for SLAM/odometry evaluation</t>
+          <t>Monado SLAM Dataset - Valve Index</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>💻🏠🤳</t>
+          <t>📸🏠🥽</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>mono, rgbd</t>
+          <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>pinhole</t>
+          <t>equid4</t>
         </is>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>https://www.doc.ic.ac.uk/~ahanda/VaFRIC/iclnuim.html</t>
+          <t>https://huggingface.co/datasets/collabora/monado-slam-datasets</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>A benchmark for RGB-D visual odometry, 3D reconstruction and SLAM</t>
+          <t>The Monado SLAM Dataset for Egocentric Visual-Inertial Tracking</t>
         </is>
       </c>
       <c r="H17" s="25" t="inlineStr">
         <is>
-          <t>https://ieeexplore.ieee.org/abstract/document/6907054</t>
+          <t>https://arxiv.org/abs/2508.00088</t>
         </is>
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="J17" s="24" t="inlineStr">
         <is>
-          <t>Ankur Handa, Thomas Whelan, John B. McDonald, Andrew J. Davison</t>
+          <t>Mateo de Mayo, Daniel Cremers, Taihú Pire</t>
         </is>
       </c>
       <c r="K17" s="24" t="inlineStr">
         <is>
-          <t>handa2014benchmark</t>
+          <t>deMayoCremersPireMSD</t>
         </is>
       </c>
       <c r="L17" s="24" t="inlineStr">
         <is>
-          <t>@inproceedings{handa2014benchmark,   title={A benchmark for RGB-D visual odometry, 3D reconstruction and SLAM},   author={Handa, Ankur and Whelan, Thomas and McDonald, John and Davison, Andrew J},   booktitle={2014 IEEE international conference on Robotics and automation (ICRA)},   pages={1524--1531},   year={2014},   organization={IEEE} }</t>
+          <t>@inproceedings{deMayoCremersPireMSD,   title={The Monado SLAM Dataset for Egocentric Visual-Inertial Tracking},   author={{de Mayo}, Mateo and Cremers, Daniel and Pire, Taih{\'u}},   booktitle={2025 IEEE/RSJ International Conference on Intelligent Robots and Systems (IROS)},   pages={13111--13118},   doi={10.1109/IROS60139.2025.11247240},   year={2025} }</t>
         </is>
       </c>
       <c r="M17" s="24" t="inlineStr">
@@ -2245,12 +2249,12 @@
       </c>
       <c r="O17" s="24" t="inlineStr">
         <is>
-          <t>tar</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="P17" s="24" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>hugging-face</t>
         </is>
       </c>
       <c r="Q17" s="24" t="inlineStr"/>
@@ -2261,69 +2265,69 @@
       </c>
       <c r="S17" s="24" t="inlineStr">
         <is>
-          <t>CC BY 3.0</t>
+          <t>CC-BY 4.0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>openloris-d400</t>
+          <t>nsavp</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>OpenLORIS-Scene - real-world lifelong SLAM dataset from real robots in real scenes</t>
+          <t>Novel Sensors for Autonomous Vehicle Perception - stereo thermal, event, monochrome and RGB cameras time-synchronized with high-precision navigation ground truth, collected from a Ford Fusion driving repeated ~8km urban routes</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>📸🏠🤳</t>
+          <t>📸🏞️🚗</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t>mono, rgbd, mono-vi, rgbd-vi</t>
+          <t>mono, stereo</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>pinhole</t>
+          <t>radtan4</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t>https://lifelong-robotic-vision.github.io/dataset/scene.html</t>
+          <t>https://umautobots.github.io/nsavp</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM</t>
+          <t>Dataset and Benchmark: Novel Sensors for Autonomous Vehicle Perception</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1911.05603</t>
+          <t>https://journals.sagepub.com/doi/abs/10.1177/02783649241273554</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t>Xuesong Shi, Others</t>
+          <t>Katherine A. Skinner, Ram Vasudevan, Manikandasriram S. Ramanagopal, Radhika Ravi, Spencer Carmichael, Austin D. Buchan</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
         <is>
-          <t>shi2020openloris</t>
+          <t>nsavp_2025</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
         <is>
-          <t>@inproceedings{shi2020openloris,   title={Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM},   author={Shi, Xuesong and Li, Dongjiang and Zhao, Pengpeng and Tian, Qinbin and Tian, Yuxin and Long, Qiwei and Zhu, Chunhao and Song, Jingwei and Qiao, Fei and Song, Le and Guo, Yangquan and Wang, Zhigang and Zhang, Yimin and Qin, Baoxing and Yang, Wei and Wang, Fangshi and Chan, Rosa H M and She, Qi},   booktitle={2020 IEEE International Conference on Robotics and Automation (ICRA)},   pages={3139--3145},   year={2020} }</t>
+          <t>@article{nsavp_2025,   title={Dataset and Benchmark: Novel Sensors for Autonomous Vehicle Perception},   author={Carmichael, Spencer and Buchan, Austin and Ramanagopal, Mani and Ravi, Radhika and Vasudevan, Ram and Skinner, Katherine A},   journal={The International Journal of Robotics Research},   volume={44},   number={3},   pages={355--365},   year={2025} }</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -2338,19 +2342,15 @@
       </c>
       <c r="O18" s="21" t="inlineStr">
         <is>
-          <t>tar, 7z</t>
+          <t>hdf5</t>
         </is>
       </c>
       <c r="P18" s="21" t="inlineStr">
         <is>
-          <t>hugging-face</t>
-        </is>
-      </c>
-      <c r="Q18" s="21" t="inlineStr">
-        <is>
-          <t>huggingface_token</t>
-        </is>
-      </c>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="Q18" s="21" t="inlineStr"/>
       <c r="R18" s="21" t="inlineStr">
         <is>
           <t>Public</t>
@@ -2358,69 +2358,69 @@
       </c>
       <c r="S18" s="21" t="inlineStr">
         <is>
-          <t>CC BY-ND 4.0</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>openloris-t265</t>
+          <t>nuim</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>OpenLORIS-Scene - real-world lifelong SLAM dataset from real robots in real scenes</t>
+          <t>ICL-NUIM RGB-D benchmark with ground-truth trajectories and 3D models for SLAM/odometry evaluation</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>📸🏠🤳</t>
+          <t>💻🏠🤳</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>mono, stereo, mono-vi, stereo-vi</t>
+          <t>mono, rgbd</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>equid4</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>https://lifelong-robotic-vision.github.io/dataset/scene.html</t>
+          <t>https://www.doc.ic.ac.uk/~ahanda/VaFRIC/iclnuim.html</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM</t>
+          <t>A benchmark for RGB-D visual odometry, 3D reconstruction and SLAM</t>
         </is>
       </c>
       <c r="H19" s="25" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1911.05603</t>
+          <t>https://ieeexplore.ieee.org/abstract/document/6907054</t>
         </is>
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="J19" s="24" t="inlineStr">
         <is>
-          <t>Xuesong Shi, Others</t>
+          <t>Ankur Handa, Thomas Whelan, John B. McDonald, Andrew J. Davison</t>
         </is>
       </c>
       <c r="K19" s="24" t="inlineStr">
         <is>
-          <t>shi2020openloris</t>
+          <t>handa2014benchmark</t>
         </is>
       </c>
       <c r="L19" s="24" t="inlineStr">
         <is>
-          <t>@inproceedings{shi2020openloris,   title={Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM},   author={Shi, Xuesong and Li, Dongjiang and Zhao, Pengpeng and Tian, Qinbin and Tian, Yuxin and Long, Qiwei and Zhu, Chunhao and Song, Jingwei and Qiao, Fei and Song, Le and Guo, Yangquan and Wang, Zhigang and Zhang, Yimin and Qin, Baoxing and Yang, Wei and Wang, Fangshi and Chan, Rosa H M and She, Qi},   booktitle={2020 IEEE International Conference on Robotics and Automation (ICRA)},   pages={3139--3145},   year={2020} }</t>
+          <t>@inproceedings{handa2014benchmark,   title={A benchmark for RGB-D visual odometry, 3D reconstruction and SLAM},   author={Handa, Ankur and Whelan, Thomas and McDonald, John and Davison, Andrew J},   booktitle={2014 IEEE international conference on Robotics and automation (ICRA)},   pages={1524--1531},   year={2014},   organization={IEEE} }</t>
         </is>
       </c>
       <c r="M19" s="24" t="inlineStr">
@@ -2435,19 +2435,15 @@
       </c>
       <c r="O19" s="24" t="inlineStr">
         <is>
-          <t>tar, 7z</t>
+          <t>tar</t>
         </is>
       </c>
       <c r="P19" s="24" t="inlineStr">
         <is>
-          <t>hugging-face</t>
-        </is>
-      </c>
-      <c r="Q19" s="24" t="inlineStr">
-        <is>
-          <t>huggingface_token</t>
-        </is>
-      </c>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="Q19" s="24" t="inlineStr"/>
       <c r="R19" s="24" t="inlineStr">
         <is>
           <t>Public</t>
@@ -2455,69 +2451,69 @@
       </c>
       <c r="S19" s="24" t="inlineStr">
         <is>
-          <t>CC BY-ND 4.0</t>
+          <t>CC BY 3.0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>pamir-rig</t>
+          <t>openloris-d400</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Multi-session visual-inertial SLAM dataset of the Pamir shipwreck (Barbados), captured with action cameras and IMU across three scuba dives</t>
+          <t>OpenLORIS-Scene - real-world lifelong SLAM dataset from real robots in real scenes</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>📸🌊🤳</t>
+          <t>📸🏠🤳</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>mono, mono-vi, stereo, stereo-vi</t>
+          <t>mono, rgbd, mono-vi, rgbd-vi</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datasets/afrl-uw/Pamir_Visual-Inertial_Data</t>
+          <t>https://lifelong-robotic-vision.github.io/dataset/scene.html</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
         <is>
-          <t>Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck</t>
+          <t>Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2607.10925</t>
+          <t>https://arxiv.org/abs/1911.05603</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
         <is>
-          <t>Michalis Chatzispyrou, Luke Horgan, Hyunkil Hwang, Harish Sathishchandra, Chinmay Burgul, Monika Roznere, Alberto Quattrini Li, Philippos Mordohai, Ioannis Rekleitis</t>
+          <t>Xuesong Shi, Others</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
         <is>
-          <t>ChatzispyrouICRA2026</t>
+          <t>shi2020openloris</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
         <is>
-          <t>@InProceedings{ChatzispyrouICRA2026,   author={Chatzispyrou, Michalis and Horgan, Luke and Hwang, Hyunkil and Sathishchandra, Harish and Burgul, Chinmay and Roznere, Monika and {Quattrini Li}, Alberto and Mordohai, Philippos and Rekleitis, Ioannis},   title={{Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck}},   booktitle={IEEE International Conference on Robotics and Automation (ICRA)},   year=2026,   month={Jun.},   address={Vienna, Austria} }</t>
+          <t>@inproceedings{shi2020openloris,   title={Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM},   author={Shi, Xuesong and Li, Dongjiang and Zhao, Pengpeng and Tian, Qinbin and Tian, Yuxin and Long, Qiwei and Zhu, Chunhao and Song, Jingwei and Qiao, Fei and Song, Le and Guo, Yangquan and Wang, Zhigang and Zhang, Yimin and Qin, Baoxing and Yang, Wei and Wang, Fangshi and Chan, Rosa H M and She, Qi},   booktitle={2020 IEEE International Conference on Robotics and Automation (ICRA)},   pages={3139--3145},   year={2020} }</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -2532,7 +2528,7 @@
       </c>
       <c r="O20" s="21" t="inlineStr">
         <is>
-          <t>ros2</t>
+          <t>tar, 7z</t>
         </is>
       </c>
       <c r="P20" s="21" t="inlineStr">
@@ -2540,7 +2536,11 @@
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="Q20" s="21" t="inlineStr"/>
+      <c r="Q20" s="21" t="inlineStr">
+        <is>
+          <t>huggingface_token</t>
+        </is>
+      </c>
       <c r="R20" s="21" t="inlineStr">
         <is>
           <t>Public</t>
@@ -2548,69 +2548,69 @@
       </c>
       <c r="S20" s="21" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>CC BY-ND 4.0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>pamir</t>
+          <t>openloris-t265</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Multi-session visual-inertial SLAM dataset of the Pamir shipwreck (Barbados), captured with action cameras and IMU across three scuba dives</t>
+          <t>OpenLORIS-Scene - real-world lifelong SLAM dataset from real robots in real scenes</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>📸🌊🤳</t>
+          <t>📸🏠🤳</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>mono, mono-vi</t>
+          <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>equid4</t>
         </is>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datasets/afrl-uw/Pamir_Visual-Inertial_Data</t>
+          <t>https://lifelong-robotic-vision.github.io/dataset/scene.html</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck</t>
+          <t>Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM</t>
         </is>
       </c>
       <c r="H21" s="25" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2607.10925</t>
+          <t>https://arxiv.org/abs/1911.05603</t>
         </is>
       </c>
       <c r="I21" s="24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="J21" s="24" t="inlineStr">
         <is>
-          <t>Michalis Chatzispyrou, Luke Horgan, Hyunkil Hwang, Harish Sathishchandra, Chinmay Burgul, Monika Roznere, Alberto Quattrini Li, Philippos Mordohai, Ioannis Rekleitis</t>
+          <t>Xuesong Shi, Others</t>
         </is>
       </c>
       <c r="K21" s="24" t="inlineStr">
         <is>
-          <t>ChatzispyrouICRA2026</t>
+          <t>shi2020openloris</t>
         </is>
       </c>
       <c r="L21" s="24" t="inlineStr">
         <is>
-          <t>@InProceedings{ChatzispyrouICRA2026,   author={Chatzispyrou, Michalis and Horgan, Luke and Hwang, Hyunkil and Sathishchandra, Harish and Burgul, Chinmay and Roznere, Monika and {Quattrini Li}, Alberto and Mordohai, Philippos and Rekleitis, Ioannis},   title={{Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck}},   booktitle={IEEE International Conference on Robotics and Automation (ICRA)},   year=2026,   month={Jun.},   address={Vienna, Austria} }</t>
+          <t>@inproceedings{shi2020openloris,   title={Are We Ready for Service Robots? The OpenLORIS-Scene Datasets for Lifelong SLAM},   author={Shi, Xuesong and Li, Dongjiang and Zhao, Pengpeng and Tian, Qinbin and Tian, Yuxin and Long, Qiwei and Zhu, Chunhao and Song, Jingwei and Qiao, Fei and Song, Le and Guo, Yangquan and Wang, Zhigang and Zhang, Yimin and Qin, Baoxing and Yang, Wei and Wang, Fangshi and Chan, Rosa H M and She, Qi},   booktitle={2020 IEEE International Conference on Robotics and Automation (ICRA)},   pages={3139--3145},   year={2020} }</t>
         </is>
       </c>
       <c r="M21" s="24" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="O21" s="24" t="inlineStr">
         <is>
-          <t>ros2</t>
+          <t>tar, 7z</t>
         </is>
       </c>
       <c r="P21" s="24" t="inlineStr">
@@ -2633,7 +2633,11 @@
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="Q21" s="24" t="inlineStr"/>
+      <c r="Q21" s="24" t="inlineStr">
+        <is>
+          <t>huggingface_token</t>
+        </is>
+      </c>
       <c r="R21" s="24" t="inlineStr">
         <is>
           <t>Public</t>
@@ -2641,69 +2645,69 @@
       </c>
       <c r="S21" s="24" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>CC BY-ND 4.0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>replica</t>
+          <t>pamir-rig</t>
         </is>
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>Photorealistic 3D indoor scene reconstructions (Replica), with RGB-D SLAM trajectories rendered by iMAP</t>
+          <t>Multi-session visual-inertial SLAM dataset of the Pamir shipwreck (Barbados), captured with action cameras and IMU across three scuba dives</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>💻🏠🤳</t>
+          <t>📸🌊🤳</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t>mono, rgbd</t>
+          <t>mono, mono-vi, stereo, stereo-vi</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>pinhole</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t>https://github.com/facebookresearch/Replica-Dataset</t>
+          <t>https://huggingface.co/datasets/afrl-uw/Pamir_Visual-Inertial_Data</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
         <is>
-          <t>The Replica Dataset: A Digital Replica of Indoor Spaces</t>
+          <t>Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1906.05797</t>
+          <t>https://arxiv.org/abs/2607.10925</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
         <is>
-          <t>Julian Straub, Thomas Whelan, Others (Replica Dataset), Edgar Sucar, Shikun Liu, Joseph Ortiz, Andrew Davison</t>
+          <t>Michalis Chatzispyrou, Luke Horgan, Hyunkil Hwang, Harish Sathishchandra, Chinmay Burgul, Monika Roznere, Alberto Quattrini Li, Philippos Mordohai, Ioannis Rekleitis</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
         <is>
-          <t>replica19arxiv</t>
+          <t>ChatzispyrouICRA2026</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
         <is>
-          <t>@article{replica19arxiv,   title =   {The {R}eplica Dataset: A Digital Replica of Indoor Spaces},   author =  {Julian Straub and Thomas Whelan and Lingni Ma and Yufan Chen and Erik Wijmans and Simon Green and Jakob J. Engel and Raul Mur-Artal and Carl Ren and Shobhit Verma and Anton Clarkson and Mingfei Yan and Brian Budge and Yajie Yan and Xiaqing Pan and June Yon and Yuyang Zou and Kimberly Leon and Nigel Carter and Jesus Briales and  Tyler Gillingham and  Elias Mueggler and Luis Pesqueira and Manolis Savva and Dhruv Batra and Hauke M. Strasdat and Renzo De Nardi and Michael Goesele and Steven Lovegrove and Richard Newcombe },   journal = {arXiv preprint arXiv:1906.05797},   year =    {2019} }</t>
+          <t>@InProceedings{ChatzispyrouICRA2026,   author={Chatzispyrou, Michalis and Horgan, Luke and Hwang, Hyunkil and Sathishchandra, Harish and Burgul, Chinmay and Roznere, Monika and {Quattrini Li}, Alberto and Mordohai, Philippos and Rekleitis, Ioannis},   title={{Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck}},   booktitle={IEEE International Conference on Robotics and Automation (ICRA)},   year=2026,   month={Jun.},   address={Vienna, Austria} }</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -2718,19 +2722,15 @@
       </c>
       <c r="O22" s="21" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>ros2</t>
         </is>
       </c>
       <c r="P22" s="21" t="inlineStr">
         <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="Q22" s="21" t="inlineStr">
-        <is>
-          <t>complete_dataset</t>
-        </is>
-      </c>
+          <t>hugging-face</t>
+        </is>
+      </c>
+      <c r="Q22" s="21" t="inlineStr"/>
       <c r="R22" s="21" t="inlineStr">
         <is>
           <t>Public</t>
@@ -2738,69 +2738,69 @@
       </c>
       <c r="S22" s="21" t="inlineStr">
         <is>
-          <t>Replica Dataset Research Terms (non-commercial research use)</t>
+          <t>License</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>rgbdtum</t>
+          <t>pamir</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>RGB-D SLAM benchmark with motion-capture ground-truth trajectories</t>
+          <t>Multi-session visual-inertial SLAM dataset of the Pamir shipwreck (Barbados), captured with action cameras and IMU across three scuba dives</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>📸🏠🤳</t>
+          <t>📸🌊🤳</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>mono, rgbd</t>
+          <t>mono, mono-vi</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>radtan5</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>https://cvg.cit.tum.de/data/datasets/rgbd-dataset</t>
+          <t>https://huggingface.co/datasets/afrl-uw/Pamir_Visual-Inertial_Data</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>A benchmark for the evaluation of RGB-D SLAM systems</t>
+          <t>Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck</t>
         </is>
       </c>
       <c r="H23" s="25" t="inlineStr">
         <is>
-          <t>https://ieeexplore.ieee.org/abstract/document/6385773</t>
+          <t>https://arxiv.org/abs/2607.10925</t>
         </is>
       </c>
       <c r="I23" s="24" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
-          <t>Jürgen Sturm, Nikolas Engelhard, Felix Endres, Wolfram Burgard, Daniel Cremers</t>
+          <t>Michalis Chatzispyrou, Luke Horgan, Hyunkil Hwang, Harish Sathishchandra, Chinmay Burgul, Monika Roznere, Alberto Quattrini Li, Philippos Mordohai, Ioannis Rekleitis</t>
         </is>
       </c>
       <c r="K23" s="24" t="inlineStr">
         <is>
-          <t>sturm2012benchmark</t>
+          <t>ChatzispyrouICRA2026</t>
         </is>
       </c>
       <c r="L23" s="24" t="inlineStr">
         <is>
-          <t>@inproceedings{sturm2012benchmark,   title={A benchmark for the evaluation of RGB-D SLAM systems},   author={Sturm, J{\"u}rgen and Engelhard, Nikolas and Endres, Felix and Burgard, Wolfram and Cremers, Daniel},   booktitle={2012 IEEE/RSJ international conference on intelligent robots and systems},   pages={573--580},   year={2012},   organization={IEEE} }</t>
+          <t>@InProceedings{ChatzispyrouICRA2026,   author={Chatzispyrou, Michalis and Horgan, Luke and Hwang, Hyunkil and Sathishchandra, Harish and Burgul, Chinmay and Roznere, Monika and {Quattrini Li}, Alberto and Mordohai, Philippos and Rekleitis, Ioannis},   title={{Mapping Pamir: Multi-Session Visual/Inertial SLAM and 3D Reconstruction of an Underwater Shipwreck}},   booktitle={IEEE International Conference on Robotics and Automation (ICRA)},   year=2026,   month={Jun.},   address={Vienna, Austria} }</t>
         </is>
       </c>
       <c r="M23" s="24" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="O23" s="24" t="inlineStr">
         <is>
-          <t>tar</t>
+          <t>ros2</t>
         </is>
       </c>
       <c r="P23" s="24" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>hugging-face</t>
         </is>
       </c>
       <c r="Q23" s="24" t="inlineStr"/>
@@ -2831,69 +2831,69 @@
       </c>
       <c r="S23" s="24" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>License</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>rover-d435i</t>
+          <t>replica</t>
         </is>
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
+          <t>Photorealistic 3D indoor scene reconstructions (Replica), with RGB-D SLAM trajectories rendered by iMAP</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>📸🏞️🤖</t>
+          <t>💻🏠🤳</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>mono, rgbd, rgbd-vi</t>
+          <t>mono, rgbd</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>radtan4</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
         <is>
-          <t>https://iis-esslingen.github.io/rover/</t>
+          <t>https://github.com/facebookresearch/Replica-Dataset</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
         <is>
-          <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
+          <t>The Replica Dataset: A Digital Replica of Indoor Spaces</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.02506</t>
+          <t>https://arxiv.org/abs/1906.05797</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
         <is>
-          <t>Fabian Schmidt, Others</t>
+          <t>Julian Straub, Thomas Whelan, Others (Replica Dataset), Edgar Sucar, Shikun Liu, Joseph Ortiz, Andrew Davison</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
         <is>
-          <t>schmidt2025rover</t>
+          <t>replica19arxiv</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
         <is>
-          <t>@article{schmidt2025rover,   title={ROVER: A Multiseason Dataset for Visual SLAM},   author={Schmidt, Fabian and Daubermann, Julian and Mitschke, Marcel and Blessing, Constantin and Meyer, Stephan and Enzweiler, Markus and Valada, Abhinav},   journal={IEEE Transactions on Robotics},   volume={41},   pages={4005--4022},   year={2025} }</t>
+          <t>@article{replica19arxiv,   title =   {The {R}eplica Dataset: A Digital Replica of Indoor Spaces},   author =  {Julian Straub and Thomas Whelan and Lingni Ma and Yufan Chen and Erik Wijmans and Simon Green and Jakob J. Engel and Raul Mur-Artal and Carl Ren and Shobhit Verma and Anton Clarkson and Mingfei Yan and Brian Budge and Yajie Yan and Xiaqing Pan and June Yon and Yuyang Zou and Kimberly Leon and Nigel Carter and Jesus Briales and  Tyler Gillingham and  Elias Mueggler and Luis Pesqueira and Manolis Savva and Dhruv Batra and Hauke M. Strasdat and Renzo De Nardi and Michael Goesele and Steven Lovegrove and Richard Newcombe },   journal = {arXiv preprint arXiv:1906.05797},   year =    {2019} }</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -2916,7 +2916,11 @@
           <t>website</t>
         </is>
       </c>
-      <c r="Q24" s="21" t="inlineStr"/>
+      <c r="Q24" s="21" t="inlineStr">
+        <is>
+          <t>complete_dataset</t>
+        </is>
+      </c>
       <c r="R24" s="21" t="inlineStr">
         <is>
           <t>Public</t>
@@ -2924,69 +2928,69 @@
       </c>
       <c r="S24" s="21" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Replica Dataset Research Terms (non-commercial research use)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>rover-picam</t>
+          <t>rgbdtum</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
+          <t>RGB-D SLAM benchmark with motion-capture ground-truth trajectories</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>📸🏞️🤖</t>
+          <t>📸🏠🤳</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>mono</t>
+          <t>mono, rgbd</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>equid4</t>
+          <t>radtan5</t>
         </is>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>https://iis-esslingen.github.io/rover/</t>
+          <t>https://cvg.cit.tum.de/data/datasets/rgbd-dataset</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
+          <t>A benchmark for the evaluation of RGB-D SLAM systems</t>
         </is>
       </c>
       <c r="H25" s="25" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2412.02506</t>
+          <t>https://ieeexplore.ieee.org/abstract/document/6385773</t>
         </is>
       </c>
       <c r="I25" s="24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="J25" s="24" t="inlineStr">
         <is>
-          <t>Fabian Schmidt, Others</t>
+          <t>Jürgen Sturm, Nikolas Engelhard, Felix Endres, Wolfram Burgard, Daniel Cremers</t>
         </is>
       </c>
       <c r="K25" s="24" t="inlineStr">
         <is>
-          <t>schmidt2025rover</t>
+          <t>sturm2012benchmark</t>
         </is>
       </c>
       <c r="L25" s="24" t="inlineStr">
         <is>
-          <t>@article{schmidt2025rover,   title={ROVER: A Multiseason Dataset for Visual SLAM},   author={Schmidt, Fabian and Daubermann, Julian and Mitschke, Marcel and Blessing, Constantin and Meyer, Stephan and Enzweiler, Markus and Valada, Abhinav},   journal={IEEE Transactions on Robotics},   volume={41},   pages={4005--4022},   year={2025} }</t>
+          <t>@inproceedings{sturm2012benchmark,   title={A benchmark for the evaluation of RGB-D SLAM systems},   author={Sturm, J{\"u}rgen and Engelhard, Nikolas and Endres, Felix and Burgard, Wolfram and Cremers, Daniel},   booktitle={2012 IEEE/RSJ international conference on intelligent robots and systems},   pages={573--580},   year={2012},   organization={IEEE} }</t>
         </is>
       </c>
       <c r="M25" s="24" t="inlineStr">
@@ -3001,7 +3005,7 @@
       </c>
       <c r="O25" s="24" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>tar</t>
         </is>
       </c>
       <c r="P25" s="24" t="inlineStr">
@@ -3017,14 +3021,14 @@
       </c>
       <c r="S25" s="24" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>rover-t265</t>
+          <t>rover-d435i</t>
         </is>
       </c>
       <c r="B26" s="21" t="inlineStr">
@@ -3039,12 +3043,12 @@
       </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
-          <t>mono, stereo, mono-vi, stereo-vi</t>
+          <t>mono, rgbd, rgbd-vi</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>equid4</t>
+          <t>radtan4</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -3117,62 +3121,62 @@
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>s3li_etna</t>
+          <t>rover-picam</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>S3LI Etna - the DLR Planetary Stereo, Solid-State LiDAR, Inertial dataset, recorded on the moon-like volcanic slopes of Mt. Etna, Sicily, for SLAM benchmarking in extremely unstructured environments</t>
+          <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>📸🏞️🪐🤳</t>
+          <t>📸🏞️🤖</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>mono, stereo, mono-vi, stereo-vi</t>
+          <t>mono</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>pinhole</t>
+          <t>equid4</t>
         </is>
       </c>
       <c r="F27" s="25" t="inlineStr">
         <is>
-          <t>https://www.dlr.de/en/rm/research/publications-and-downloads/datasets/s3li-datasets</t>
+          <t>https://iis-esslingen.github.io/rover/</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>Challenges of SLAM in extremely unstructured environments: the DLR Planetary Stereo, Solid-State LiDAR, Inertial Dataset</t>
+          <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
         </is>
       </c>
       <c r="H27" s="25" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/LRA.2022.3188118</t>
+          <t>https://arxiv.org/abs/2412.02506</t>
         </is>
       </c>
       <c r="I27" s="24" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="J27" s="24" t="inlineStr">
         <is>
-          <t>Riccardo Giubilato, Wolfgang Stürzl, Armin Wedler, Rudolph Triebel</t>
+          <t>Fabian Schmidt, Others</t>
         </is>
       </c>
       <c r="K27" s="24" t="inlineStr">
         <is>
-          <t>giubilato2022challenges</t>
+          <t>schmidt2025rover</t>
         </is>
       </c>
       <c r="L27" s="24" t="inlineStr">
         <is>
-          <t>@article{giubilato2022challenges,   title={Challenges of SLAM in extremely unstructured environments: the DLR Planetary Stereo, Solid-State LiDAR, Inertial Dataset},   author={Giubilato, Riccardo and St{\"u}rzl, Wolfgang and Wedler, Armin and Triebel, Rudolph},   journal={IEEE Robotics and Automation Letters},   volume={7},   number={4},   pages={8721--8728},   publisher={IEEE},   year={2022} }</t>
+          <t>@article{schmidt2025rover,   title={ROVER: A Multiseason Dataset for Visual SLAM},   author={Schmidt, Fabian and Daubermann, Julian and Mitschke, Marcel and Blessing, Constantin and Meyer, Stephan and Enzweiler, Markus and Valada, Abhinav},   journal={IEEE Transactions on Robotics},   volume={41},   pages={4005--4022},   year={2025} }</t>
         </is>
       </c>
       <c r="M27" s="24" t="inlineStr">
@@ -3203,24 +3207,24 @@
       </c>
       <c r="S27" s="24" t="inlineStr">
         <is>
-          <t>Not explicitly stated by DLR (research/academic use)</t>
+          <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>s3li_vulcano</t>
+          <t>rover-t265</t>
         </is>
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>S3LI Vulcano - a multi-modal (RGB stereo, solid-state LiDAR, inertial) dataset for SLAM and place recognition in unstructured planetary-analogue environments, recorded on the volcanic island of Vulcano, Sicily</t>
+          <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>📸🏞️🪐🤳</t>
+          <t>📸🏞️🤖</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -3230,42 +3234,42 @@
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>pinhole</t>
+          <t>equid4</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
         <is>
-          <t>https://www.dlr.de/en/rm/research/publications-and-downloads/datasets/s3li-datasets</t>
+          <t>https://iis-esslingen.github.io/rover/</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>The S3LI Vulcano Dataset: A Dataset for Multi-Modal SLAM in Unstructured Planetary Environments</t>
+          <t>ROVER: A Multiseason Dataset for Visual SLAM</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2601.19557</t>
+          <t>https://arxiv.org/abs/2412.02506</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
         <is>
-          <t>Riccardo Giubilato, Marcus Gerhard Müller, Marco Sewtz, Laura Alejandra Encinar Gonzalez, John Folkesson, Rudolph Triebel</t>
+          <t>Fabian Schmidt, Others</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
         <is>
-          <t>giubilato2026s3livulcano</t>
+          <t>schmidt2025rover</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
         <is>
-          <t>@misc{giubilato2026s3livulcano,   title={The S3LI Vulcano Dataset: A Dataset for Multi-Modal SLAM in Unstructured Planetary Environments},   author={Giubilato, Riccardo and M{\"u}ller, Marcus Gerhard and Sewtz, Marco and Encinar Gonzalez, Laura Alejandra and Folkesson, John and Triebel, Rudolph},   eprint={2601.19557},   archivePrefix={arXiv},   year={2026} }</t>
+          <t>@article{schmidt2025rover,   title={ROVER: A Multiseason Dataset for Visual SLAM},   author={Schmidt, Fabian and Daubermann, Julian and Mitschke, Marcel and Blessing, Constantin and Meyer, Stephan and Enzweiler, Markus and Valada, Abhinav},   journal={IEEE Transactions on Robotics},   volume={41},   pages={4005--4022},   year={2025} }</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -3296,69 +3300,69 @@
       </c>
       <c r="S28" s="21" t="inlineStr">
         <is>
-          <t>Not explicitly stated by DLR (research/academic use)</t>
+          <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>sesoko</t>
+          <t>rvp-car</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>AUV (TUNA-SAND) coral-reef mapping surveys off Sesoko Island, Okinawa, Japan (2016-2018 campaigns), served via the SQUIDLE+ marine imagery platform</t>
+          <t>VBR - A Vision Benchmark in Rome (car sequences) - hardware-synced stereo camera, solid-state LiDAR and IMU data around Sapienza's main Campus and the town of Ciampino</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>📸🏞️🌊</t>
+          <t>📸🏞️🚗</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>mono</t>
+          <t>mono, mono-vi, stereo, stereo-vi</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>radtan4</t>
         </is>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>https://squidle.org/</t>
+          <t>https://rvp-group.net/slam-dataset.html</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VBR: A Vision Benchmark in Rome</t>
         </is>
       </c>
       <c r="H29" s="25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://arxiv.org/abs/2404.11322</t>
         </is>
       </c>
       <c r="I29" s="24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="J29" s="24" t="inlineStr">
         <is>
-          <t>Blair Thornton, Toshihiro Maki, Saki Harii, Oscar Pizarro, Kazuo Nishida</t>
+          <t>Leonardo Brizi, Emanuele Giacomini, Luca Di Giammarino, Simone Ferrari, Omar Salem, Lorenzo De Rebotti, Giorgio Grisetti</t>
         </is>
       </c>
       <c r="K29" s="24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>brizi2024vbr</t>
         </is>
       </c>
       <c r="L29" s="24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>@inproceedings{brizi2024vbr,   title={VBR: A vision benchmark in Rome},   author={Brizi, Leonardo and Giacomini, Emanuele and Di Giammarino, Luca and Ferrari, Simone and Salem, Omar and De Rebotti, Lorenzo and Grisetti, Giorgio},   booktitle={2024 IEEE International Conference on Robotics and Automation (ICRA)},   pages={15868--15874},   year={2024},   organization={IEEE} }</t>
         </is>
       </c>
       <c r="M29" s="24" t="inlineStr">
@@ -3373,89 +3377,85 @@
       </c>
       <c r="O29" s="24" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>ros1</t>
         </is>
       </c>
       <c r="P29" s="24" t="inlineStr">
         <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="Q29" s="24" t="inlineStr">
-        <is>
-          <t>api_token</t>
-        </is>
-      </c>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="Q29" s="24" t="inlineStr"/>
       <c r="R29" s="24" t="inlineStr">
         <is>
-          <t>Registration Required</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="S29" s="24" t="inlineStr">
         <is>
-          <t>No explicit license stated by SQUIDLE+ or the source surveys; imagery served via the SQUIDLE+ platform (squidle.org)</t>
+          <t>CC BY-SA 4.0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>soneva</t>
+          <t>rvp-handheld</t>
         </is>
       </c>
       <c r="B30" s="21" t="inlineStr">
         <is>
-          <t>Coral reef time-series photogrammetry (Maldives), from Soneva Conservation and Sustainability Maldives and Wildflow</t>
+          <t>VBR - A Vision Benchmark in Rome (hand-held sequences) - hardware-synced stereo camera, solid-state LiDAR and IMU data around the Colosseum, Piazza di Spagna, Villa Borghese (Pincio) and Sapienza's DIAG building</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
         <is>
-          <t>📸🏞️🌊🤳</t>
+          <t>📸🏞️🤳</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>mono</t>
+          <t>mono, mono-vi, stereo, stereo-vi</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>pinhole</t>
+          <t>radtan4</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datasets/wildflow/soneva-corals</t>
+          <t>https://rvp-group.net/slam-dataset.html</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>VBR: A Vision Benchmark in Rome</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://arxiv.org/abs/2404.11322</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
         <is>
-          <t>Ben Yuen, Ayla Kroon, Tom Freer, Ashley Wallis, Johanna Leonhardt, Wildflow</t>
+          <t>Leonardo Brizi, Emanuele Giacomini, Luca Di Giammarino, Simone Ferrari, Omar Salem, Lorenzo De Rebotti, Giorgio Grisetti</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>brizi2024vbr</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>@inproceedings{brizi2024vbr,   title={VBR: A vision benchmark in Rome},   author={Brizi, Leonardo and Giacomini, Emanuele and Di Giammarino, Luca and Ferrari, Simone and Salem, Omar and De Rebotti, Lorenzo and Grisetti, Giorgio},   booktitle={2024 IEEE International Conference on Robotics and Automation (ICRA)},   pages={15868--15874},   year={2024},   organization={IEEE} }</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -3470,19 +3470,15 @@
       </c>
       <c r="O30" s="21" t="inlineStr">
         <is>
-          <t>images, colmap</t>
+          <t>ros1</t>
         </is>
       </c>
       <c r="P30" s="21" t="inlineStr">
         <is>
-          <t>hugging-face</t>
-        </is>
-      </c>
-      <c r="Q30" s="21" t="inlineStr">
-        <is>
-          <t>huggingface_token</t>
-        </is>
-      </c>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="Q30" s="21" t="inlineStr"/>
       <c r="R30" s="21" t="inlineStr">
         <is>
           <t>Public</t>
@@ -3490,29 +3486,29 @@
       </c>
       <c r="S30" s="21" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>CC BY-SA 4.0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>strayscanner</t>
+          <t>s3li-etna</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>An app for collecting raw RGB-D scans on iOS devices.</t>
+          <t>S3LI Etna - the DLR Planetary Stereo, Solid-State LiDAR, Inertial dataset, recorded on the moon-like volcanic slopes of Mt. Etna, Sicily, for SLAM benchmarking in extremely unstructured environments</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>📸🤳</t>
+          <t>📸🏞️🪐🤳</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>mono, rgbd</t>
+          <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -3522,53 +3518,57 @@
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>https://docs.strayrobots.io/</t>
+          <t>https://www.dlr.de/en/rm/research/publications-and-downloads/datasets/s3li-datasets</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Challenges of SLAM in extremely unstructured environments: the DLR Planetary Stereo, Solid-State LiDAR, Inertial Dataset</t>
         </is>
       </c>
       <c r="H31" s="25" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://doi.org/10.1109/LRA.2022.3188118</t>
         </is>
       </c>
       <c r="I31" s="24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="J31" s="24" t="inlineStr">
         <is>
-          <t>Kenneth Blomqvist, Martin Smith, Sihat Afnan</t>
+          <t>Riccardo Giubilato, Wolfgang Stürzl, Armin Wedler, Rudolph Triebel</t>
         </is>
       </c>
       <c r="K31" s="24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>giubilato2022challenges</t>
         </is>
       </c>
       <c r="L31" s="24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>@article{giubilato2022challenges,   title={Challenges of SLAM in extremely unstructured environments: the DLR Planetary Stereo, Solid-State LiDAR, Inertial Dataset},   author={Giubilato, Riccardo and St{\"u}rzl, Wolfgang and Wedler, Armin and Triebel, Rudolph},   journal={IEEE Robotics and Automation Letters},   volume={7},   number={4},   pages={8721--8728},   publisher={IEEE},   year={2022} }</t>
         </is>
       </c>
       <c r="M31" s="24" t="inlineStr">
         <is>
-          <t>Nicolas Marticorena</t>
-        </is>
-      </c>
-      <c r="N31" s="24" t="inlineStr"/>
+          <t>Alejandro Fontan</t>
+        </is>
+      </c>
+      <c r="N31" s="24" t="inlineStr">
+        <is>
+          <t>Claude (Sonnet 5)</t>
+        </is>
+      </c>
       <c r="O31" s="24" t="inlineStr">
         <is>
-          <t>zip, video, local</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="P31" s="24" t="inlineStr">
         <is>
-          <t>hugging-face, local</t>
+          <t>website</t>
         </is>
       </c>
       <c r="Q31" s="24" t="inlineStr"/>
@@ -3579,69 +3579,69 @@
       </c>
       <c r="S31" s="24" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Not explicitly stated by DLR (research/academic use)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>sweetcorals</t>
+          <t>s3li-vulcano</t>
         </is>
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>Coral reef 3D photogrammetry (Indonesia), from Wildflow</t>
+          <t>S3LI Vulcano - a multi-modal (RGB stereo, solid-state LiDAR, inertial) dataset for SLAM and place recognition in unstructured planetary-analogue environments, recorded on the volcanic island of Vulcano, Sicily</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
         <is>
-          <t>📸🏞️🌊🤳</t>
+          <t>📸🏞️🪐🤳</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
-          <t>mono</t>
+          <t>mono, stereo, mono-vi, stereo-vi</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
         <is>
-          <t>pinhole, unknown</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datasets/wildflow/sweet-corals</t>
+          <t>https://www.dlr.de/en/rm/research/publications-and-downloads/datasets/s3li-datasets</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The S3LI Vulcano Dataset: A Dataset for Multi-Modal SLAM in Unstructured Planetary Environments</t>
         </is>
       </c>
       <c r="H32" s="22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://arxiv.org/abs/2601.19557</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr">
         <is>
-          <t>Sergei Nozdrenkov, Michael Sweet, University of Derby, BRIN (Indonesia), Coral Spawning Lab, Wildflow, CORDAP</t>
+          <t>Riccardo Giubilato, Marcus Gerhard Müller, Marco Sewtz, Laura Alejandra Encinar Gonzalez, John Folkesson, Rudolph Triebel</t>
         </is>
       </c>
       <c r="K32" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>giubilato2026s3livulcano</t>
         </is>
       </c>
       <c r="L32" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>@misc{giubilato2026s3livulcano,   title={The S3LI Vulcano Dataset: A Dataset for Multi-Modal SLAM in Unstructured Planetary Environments},   author={Giubilato, Riccardo and M{\"u}ller, Marcus Gerhard and Sewtz, Marco and Encinar Gonzalez, Laura Alejandra and Folkesson, John and Triebel, Rudolph},   eprint={2601.19557},   archivePrefix={arXiv},   year={2026} }</t>
         </is>
       </c>
       <c r="M32" s="21" t="inlineStr">
@@ -3656,19 +3656,15 @@
       </c>
       <c r="O32" s="21" t="inlineStr">
         <is>
-          <t>images, colmap</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="P32" s="21" t="inlineStr">
         <is>
-          <t>hugging-face</t>
-        </is>
-      </c>
-      <c r="Q32" s="21" t="inlineStr">
-        <is>
-          <t>huggingface_token</t>
-        </is>
-      </c>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="Q32" s="21" t="inlineStr"/>
       <c r="R32" s="21" t="inlineStr">
         <is>
           <t>Public</t>
@@ -3676,24 +3672,24 @@
       </c>
       <c r="S32" s="21" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>Not explicitly stated by DLR (research/academic use)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>tartanair</t>
+          <t>sesoko</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Large-scale photorealistic simulation dataset with multimodal ground truth for SLAM under challenging conditions</t>
+          <t>AUV (TUNA-SAND) coral-reef mapping surveys off Sesoko Island, Okinawa, Japan (2016-2018 campaigns), served via the SQUIDLE+ marine imagery platform</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>💻🏞️🤳</t>
+          <t>📸🏞️🌊</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
@@ -3703,42 +3699,42 @@
       </c>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>pinhole</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>https://theairlab.org/tartanair-dataset/</t>
+          <t>https://squidle.org/</t>
         </is>
       </c>
       <c r="G33" s="24" t="inlineStr">
         <is>
-          <t>TartanAir: A Dataset to Push the Limits of Visual SLAM</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H33" s="25" t="inlineStr">
         <is>
-          <t>https://ieeexplore.ieee.org/abstract/document/9341801</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I33" s="24" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J33" s="24" t="inlineStr">
         <is>
-          <t>Wenshan Wang, Delong Zhu, Xiangwei Wang, Yaoyu Hu, Yuheng Qiu, Chen Wang, Yafei Hu, Ashish Kapoor, Sebastian Scherer</t>
+          <t>Blair Thornton, Toshihiro Maki, Saki Harii, Oscar Pizarro, Kazuo Nishida</t>
         </is>
       </c>
       <c r="K33" s="24" t="inlineStr">
         <is>
-          <t>tartanair2020iros</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L33" s="24" t="inlineStr">
         <is>
-          <t>@article{tartanair2020iros,   title =   {TartanAir: A Dataset to Push the Limits of Visual SLAM},   author =  {Wang, Wenshan and Zhu, Delong and Wang, Xiangwei and Hu, Yaoyu and Qiu, Yuheng and Wang, Chen and Hu, Yafei and Kapoor, Ashish and Scherer, Sebastian},   booktitle = {2020 IEEE/RSJ International Conference on Intelligent Robots and Systems (IROS)},   year =    {2020} }</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M33" s="24" t="inlineStr">
@@ -3753,89 +3749,89 @@
       </c>
       <c r="O33" s="24" t="inlineStr">
         <is>
-          <t>tar, zip</t>
+          <t>images</t>
         </is>
       </c>
       <c r="P33" s="24" t="inlineStr">
         <is>
-          <t>website</t>
+          <t>api</t>
         </is>
       </c>
       <c r="Q33" s="24" t="inlineStr">
         <is>
-          <t>complete_dataset</t>
+          <t>api_token</t>
         </is>
       </c>
       <c r="R33" s="24" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Registration Required</t>
         </is>
       </c>
       <c r="S33" s="24" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>No explicit license stated by SQUIDLE+ or the source surveys; imagery served via the SQUIDLE+ platform (squidle.org)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>ut-coda</t>
+          <t>soneva</t>
         </is>
       </c>
       <c r="B34" s="21" t="inlineStr">
         <is>
-          <t>The UT Campus Object Dataset (CODa) - egocentric robot perception dataset collected on the UT Austin campus</t>
+          <t>Coral reef time-series photogrammetry (Maldives), from Soneva Conservation and Sustainability Maldives and Wildflow</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>📸🏞️🤖</t>
+          <t>📸🏞️🌊🤳</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>mono, stereo</t>
+          <t>mono</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>radtan5</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
         <is>
-          <t>https://amrl.cs.utexas.edu/coda/</t>
+          <t>https://huggingface.co/datasets/wildflow/soneva-corals</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
         <is>
-          <t>Toward Robust Robot 3-D Perception in Urban Environments: The UT Campus Object Dataset</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H34" s="22" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/TRO.2024.3400831</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J34" s="21" t="inlineStr">
         <is>
-          <t>Arthur Zhang, Joydeep Biswas, Others</t>
+          <t>Ben Yuen, Ayla Kroon, Tom Freer, Ashley Wallis, Johanna Leonhardt, Wildflow</t>
         </is>
       </c>
       <c r="K34" s="21" t="inlineStr">
         <is>
-          <t>zhang2024coda</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L34" s="21" t="inlineStr">
         <is>
-          <t>@article{zhang2024coda,   title={Toward Robust Robot 3-D Perception in Urban Environments: The UT Campus Object Dataset},   author={Zhang, Arthur and Eranki, Chaitanya and Zhang, Christina and Park, Ji-Hwan and Hong, Raymond and Kalyani, Pranav and Kalyanaraman, Lochana and Gamare, Arsh and Bagad, Arnav and Esteva, Maria and Biswas, Joydeep},   journal={IEEE Transactions on Robotics},   volume={40},   publisher={IEEE},   year={2024} }</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M34" s="21" t="inlineStr">
@@ -3850,15 +3846,19 @@
       </c>
       <c r="O34" s="21" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>images, colmap</t>
         </is>
       </c>
       <c r="P34" s="21" t="inlineStr">
         <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="Q34" s="21" t="inlineStr"/>
+          <t>hugging-face</t>
+        </is>
+      </c>
+      <c r="Q34" s="21" t="inlineStr">
+        <is>
+          <t>huggingface_token</t>
+        </is>
+      </c>
       <c r="R34" s="21" t="inlineStr">
         <is>
           <t>Public</t>
@@ -3866,89 +3866,85 @@
       </c>
       <c r="S34" s="21" t="inlineStr">
         <is>
-          <t>CC BY-NC-SA 4.0</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>vector</t>
+          <t>strayscanner</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>VECtor - a versatile event-centric benchmark for multi-sensor SLAM, with a regular stereo camera, an event stereo camera, an RGB-D sensor, a LiDAR and an IMU, covering small-scale (motion-capture ground truth) and large-scale (LiDAR-ICP ground truth) indoor sequences</t>
+          <t>An app for collecting raw RGB-D scans on iOS devices.</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>📸🏠🤳🤖</t>
+          <t>📸🤳</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>mono, stereo, mono-vi, stereo-vi</t>
+          <t>mono, rgbd</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>radtan4</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>https://star-datasets.github.io/vector/</t>
+          <t>https://docs.strayrobots.io/</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>VECtor: A Versatile Event-Centric Benchmark for Multi-Sensor SLAM</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H35" s="25" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2207.01404</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I35" s="24" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J35" s="24" t="inlineStr">
         <is>
-          <t>Ling Gao, Yuxuan Liang, Jiaqi Yang, Shaoxun Wu, Chenyu Wang, Jiaben Chen, Laurent Kneip</t>
+          <t>Kenneth Blomqvist, Martin Smith, Sihat Afnan</t>
         </is>
       </c>
       <c r="K35" s="24" t="inlineStr">
         <is>
-          <t>gao2022vector</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L35" s="24" t="inlineStr">
         <is>
-          <t>@article{gao2022vector,   title={VECtor: A Versatile Event-Centric Benchmark for Multi-Sensor SLAM},   author={Gao, Ling and Liang, Yuxuan and Yang, Jiaqi and Wu, Shaoxun and Wang, Chenyu and Chen, Jiaben and Kneip, Laurent},   journal={IEEE Robotics and Automation Letters},   volume={7},   number={3},   pages={8217--8224},   publisher={IEEE},   year={2022} }</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M35" s="24" t="inlineStr">
         <is>
-          <t>Alejandro Fontan</t>
-        </is>
-      </c>
-      <c r="N35" s="24" t="inlineStr">
-        <is>
-          <t>Claude (Sonnet 5)</t>
-        </is>
-      </c>
+          <t>Nicolas Marticorena</t>
+        </is>
+      </c>
+      <c r="N35" s="24" t="inlineStr"/>
       <c r="O35" s="24" t="inlineStr">
         <is>
-          <t>zip</t>
+          <t>zip, video, local</t>
         </is>
       </c>
       <c r="P35" s="24" t="inlineStr">
         <is>
-          <t>google-drive</t>
+          <t>hugging-face, local</t>
         </is>
       </c>
       <c r="Q35" s="24" t="inlineStr"/>
@@ -3959,22 +3955,26 @@
       </c>
       <c r="S35" s="24" t="inlineStr">
         <is>
-          <t>BSD-3-Clause Clear License</t>
+          <t>MIT</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>sweetcorals</t>
         </is>
       </c>
       <c r="B36" s="21" t="inlineStr">
         <is>
-          <t>Videos recorded for VSLAM-LAB</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="inlineStr"/>
+          <t>Coral reef 3D photogrammetry (Indonesia), from Wildflow</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>📸🏞️🌊🤳</t>
+        </is>
+      </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
           <t>mono</t>
@@ -3982,12 +3982,12 @@
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>unknown, pinhole</t>
+          <t>pinhole, unknown</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
         <is>
-          <t>https://huggingface.co/datasets/vslamlab/videos</t>
+          <t>https://huggingface.co/datasets/wildflow/sweet-corals</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -4007,32 +4007,32 @@
       </c>
       <c r="J36" s="21" t="inlineStr">
         <is>
+          <t>Sergei Nozdrenkov, Michael Sweet, University of Derby, BRIN (Indonesia), Coral Spawning Lab, Wildflow, CORDAP</t>
+        </is>
+      </c>
+      <c r="K36" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L36" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M36" s="21" t="inlineStr">
+        <is>
           <t>Alejandro Fontan</t>
         </is>
       </c>
-      <c r="K36" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L36" s="21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M36" s="21" t="inlineStr">
-        <is>
-          <t>Alejandro Fontan</t>
-        </is>
-      </c>
       <c r="N36" s="21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Claude (Sonnet 5)</t>
         </is>
       </c>
       <c r="O36" s="21" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>images, colmap</t>
         </is>
       </c>
       <c r="P36" s="21" t="inlineStr">
@@ -4040,7 +4040,11 @@
           <t>hugging-face</t>
         </is>
       </c>
-      <c r="Q36" s="21" t="inlineStr"/>
+      <c r="Q36" s="21" t="inlineStr">
+        <is>
+          <t>huggingface_token</t>
+        </is>
+      </c>
       <c r="R36" s="21" t="inlineStr">
         <is>
           <t>Public</t>
@@ -4048,69 +4052,69 @@
       </c>
       <c r="S36" s="21" t="inlineStr">
         <is>
-          <t>GPLv3 License</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>vitum</t>
+          <t>tartanair</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>TUM Visual-Inertial Dataset - stereo fisheye and IMU sequences from a handheld rig, with motion-capture ground truth, for visual-inertial odometry/SLAM evaluation</t>
+          <t>Large-scale photorealistic simulation dataset with multimodal ground truth for SLAM under challenging conditions</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>📸🏠🏞️🤳</t>
+          <t>💻🏞️🤳</t>
         </is>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>mono, mono-vi, stereo, stereo-vi</t>
+          <t>mono</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>equid4</t>
+          <t>pinhole</t>
         </is>
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>https://cvg.cit.tum.de/data/datasets/visual-inertial-dataset</t>
+          <t>https://theairlab.org/tartanair-dataset/</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
         <is>
-          <t>The TUM VI Benchmark for Evaluating Visual-Inertial Odometry</t>
+          <t>TartanAir: A Dataset to Push the Limits of Visual SLAM</t>
         </is>
       </c>
       <c r="H37" s="25" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/1804.06120</t>
+          <t>https://ieeexplore.ieee.org/abstract/document/9341801</t>
         </is>
       </c>
       <c r="I37" s="24" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="J37" s="24" t="inlineStr">
         <is>
-          <t>David Schubert, Thore Goll, Nikolaus Demmel, Vladyslav Usenko, Jörg Stückler, Daniel Cremers</t>
+          <t>Wenshan Wang, Delong Zhu, Xiangwei Wang, Yaoyu Hu, Yuheng Qiu, Chen Wang, Yafei Hu, Ashish Kapoor, Sebastian Scherer</t>
         </is>
       </c>
       <c r="K37" s="24" t="inlineStr">
         <is>
-          <t>schubert2018vidataset</t>
+          <t>tartanair2020iros</t>
         </is>
       </c>
       <c r="L37" s="24" t="inlineStr">
         <is>
-          <t>@inproceedings{schubert2018vidataset,   title={The TUM VI Benchmark for Evaluating Visual-Inertial Odometry},   author={Schubert, D. and Goll, T. and Demmel, N. and Usenko, V. and Stueckler, J. and Cremers, D.},   booktitle={International Conference on Intelligent Robots and Systems (IROS)},   year={2018} }</t>
+          <t>@article{tartanair2020iros,   title =   {TartanAir: A Dataset to Push the Limits of Visual SLAM},   author =  {Wang, Wenshan and Zhu, Delong and Wang, Xiangwei and Hu, Yaoyu and Qiu, Yuheng and Wang, Chen and Hu, Yafei and Kapoor, Ashish and Scherer, Sebastian},   booktitle = {2020 IEEE/RSJ International Conference on Intelligent Robots and Systems (IROS)},   year =    {2020} }</t>
         </is>
       </c>
       <c r="M37" s="24" t="inlineStr">
@@ -4125,7 +4129,7 @@
       </c>
       <c r="O37" s="24" t="inlineStr">
         <is>
-          <t>tar</t>
+          <t>tar, zip</t>
         </is>
       </c>
       <c r="P37" s="24" t="inlineStr">
@@ -4133,7 +4137,11 @@
           <t>website</t>
         </is>
       </c>
-      <c r="Q37" s="24" t="inlineStr"/>
+      <c r="Q37" s="24" t="inlineStr">
+        <is>
+          <t>complete_dataset</t>
+        </is>
+      </c>
       <c r="R37" s="24" t="inlineStr">
         <is>
           <t>Public</t>
@@ -4148,58 +4156,62 @@
     <row r="38">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>ut-coda</t>
         </is>
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>Youtube videos of VSLAM sequences.</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr"/>
+          <t>The UT Campus Object Dataset (CODa) - egocentric robot perception dataset collected on the UT Austin campus</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>📸🏞️🤖</t>
+        </is>
+      </c>
       <c r="D38" s="21" t="inlineStr">
         <is>
-          <t>mono</t>
+          <t>mono, stereo</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>radtan4, unknown</t>
+          <t>radtan5</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
         <is>
-          <t>https://youtu.be/kcfs1-ryKWE</t>
+          <t>https://amrl.cs.utexas.edu/coda/</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Toward Robust Robot 3-D Perception in Urban Environments: The UT Campus Object Dataset</t>
         </is>
       </c>
       <c r="H38" s="22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>https://doi.org/10.1109/TRO.2024.3400831</t>
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="J38" s="21" t="inlineStr">
         <is>
-          <t>Unknown uploader</t>
+          <t>Arthur Zhang, Joydeep Biswas, Others</t>
         </is>
       </c>
       <c r="K38" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>zhang2024coda</t>
         </is>
       </c>
       <c r="L38" s="21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>@article{zhang2024coda,   title={Toward Robust Robot 3-D Perception in Urban Environments: The UT Campus Object Dataset},   author={Zhang, Arthur and Eranki, Chaitanya and Zhang, Christina and Park, Ji-Hwan and Hong, Raymond and Kalyani, Pranav and Kalyanaraman, Lochana and Gamare, Arsh and Bagad, Arnav and Esteva, Maria and Biswas, Joydeep},   journal={IEEE Transactions on Robotics},   volume={40},   publisher={IEEE},   year={2024} }</t>
         </is>
       </c>
       <c r="M38" s="21" t="inlineStr">
@@ -4209,12 +4221,12 @@
       </c>
       <c r="N38" s="21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Claude (Sonnet 5)</t>
         </is>
       </c>
       <c r="O38" s="21" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>zip</t>
         </is>
       </c>
       <c r="P38" s="21" t="inlineStr">
@@ -4229,6 +4241,370 @@
         </is>
       </c>
       <c r="S38" s="21" t="inlineStr">
+        <is>
+          <t>CC BY-NC-SA 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>vector</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>VECtor - a versatile event-centric benchmark for multi-sensor SLAM, with a regular stereo camera, an event stereo camera, an RGB-D sensor, a LiDAR and an IMU, covering small-scale (motion-capture ground truth) and large-scale (LiDAR-ICP ground truth) indoor sequences</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>📸🏠🤳🤖</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>mono, stereo, mono-vi, stereo-vi</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>radtan4</t>
+        </is>
+      </c>
+      <c r="F39" s="25" t="inlineStr">
+        <is>
+          <t>https://star-datasets.github.io/vector/</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>VECtor: A Versatile Event-Centric Benchmark for Multi-Sensor SLAM</t>
+        </is>
+      </c>
+      <c r="H39" s="25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2207.01404</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J39" s="24" t="inlineStr">
+        <is>
+          <t>Ling Gao, Yuxuan Liang, Jiaqi Yang, Shaoxun Wu, Chenyu Wang, Jiaben Chen, Laurent Kneip</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>gao2022vector</t>
+        </is>
+      </c>
+      <c r="L39" s="24" t="inlineStr">
+        <is>
+          <t>@article{gao2022vector,   title={VECtor: A Versatile Event-Centric Benchmark for Multi-Sensor SLAM},   author={Gao, Ling and Liang, Yuxuan and Yang, Jiaqi and Wu, Shaoxun and Wang, Chenyu and Chen, Jiaben and Kneip, Laurent},   journal={IEEE Robotics and Automation Letters},   volume={7},   number={3},   pages={8217--8224},   publisher={IEEE},   year={2022} }</t>
+        </is>
+      </c>
+      <c r="M39" s="24" t="inlineStr">
+        <is>
+          <t>Alejandro Fontan</t>
+        </is>
+      </c>
+      <c r="N39" s="24" t="inlineStr">
+        <is>
+          <t>Claude (Sonnet 5)</t>
+        </is>
+      </c>
+      <c r="O39" s="24" t="inlineStr">
+        <is>
+          <t>zip</t>
+        </is>
+      </c>
+      <c r="P39" s="24" t="inlineStr">
+        <is>
+          <t>google-drive</t>
+        </is>
+      </c>
+      <c r="Q39" s="24" t="inlineStr"/>
+      <c r="R39" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S39" s="24" t="inlineStr">
+        <is>
+          <t>BSD-3-Clause Clear License</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>videos</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>Videos recorded for VSLAM-LAB</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr"/>
+      <c r="D40" s="21" t="inlineStr">
+        <is>
+          <t>mono</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="inlineStr">
+        <is>
+          <t>unknown, pinhole</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/datasets/vslamlab/videos</t>
+        </is>
+      </c>
+      <c r="G40" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I40" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J40" s="21" t="inlineStr">
+        <is>
+          <t>Alejandro Fontan</t>
+        </is>
+      </c>
+      <c r="K40" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L40" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M40" s="21" t="inlineStr">
+        <is>
+          <t>Alejandro Fontan</t>
+        </is>
+      </c>
+      <c r="N40" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O40" s="21" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="P40" s="21" t="inlineStr">
+        <is>
+          <t>hugging-face</t>
+        </is>
+      </c>
+      <c r="Q40" s="21" t="inlineStr"/>
+      <c r="R40" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S40" s="21" t="inlineStr">
+        <is>
+          <t>GPLv3 License</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>vitum</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>TUM Visual-Inertial Dataset - stereo fisheye and IMU sequences from a handheld rig, with motion-capture ground truth, for visual-inertial odometry/SLAM evaluation</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>📸🏠🏞️🤳</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>mono, mono-vi, stereo, stereo-vi</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>equid4</t>
+        </is>
+      </c>
+      <c r="F41" s="25" t="inlineStr">
+        <is>
+          <t>https://cvg.cit.tum.de/data/datasets/visual-inertial-dataset</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>The TUM VI Benchmark for Evaluating Visual-Inertial Odometry</t>
+        </is>
+      </c>
+      <c r="H41" s="25" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/1804.06120</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="J41" s="24" t="inlineStr">
+        <is>
+          <t>David Schubert, Thore Goll, Nikolaus Demmel, Vladyslav Usenko, Jörg Stückler, Daniel Cremers</t>
+        </is>
+      </c>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>schubert2018vidataset</t>
+        </is>
+      </c>
+      <c r="L41" s="24" t="inlineStr">
+        <is>
+          <t>@inproceedings{schubert2018vidataset,   title={The TUM VI Benchmark for Evaluating Visual-Inertial Odometry},   author={Schubert, D. and Goll, T. and Demmel, N. and Usenko, V. and Stueckler, J. and Cremers, D.},   booktitle={International Conference on Intelligent Robots and Systems (IROS)},   year={2018} }</t>
+        </is>
+      </c>
+      <c r="M41" s="24" t="inlineStr">
+        <is>
+          <t>Alejandro Fontan</t>
+        </is>
+      </c>
+      <c r="N41" s="24" t="inlineStr">
+        <is>
+          <t>Claude (Sonnet 5)</t>
+        </is>
+      </c>
+      <c r="O41" s="24" t="inlineStr">
+        <is>
+          <t>tar</t>
+        </is>
+      </c>
+      <c r="P41" s="24" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="Q41" s="24" t="inlineStr"/>
+      <c r="R41" s="24" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S41" s="24" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Youtube videos of VSLAM sequences.</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr"/>
+      <c r="D42" s="21" t="inlineStr">
+        <is>
+          <t>mono</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="inlineStr">
+        <is>
+          <t>radtan4, unknown</t>
+        </is>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>https://youtu.be/kcfs1-ryKWE</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H42" s="22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I42" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J42" s="21" t="inlineStr">
+        <is>
+          <t>Unknown uploader</t>
+        </is>
+      </c>
+      <c r="K42" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L42" s="21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M42" s="21" t="inlineStr">
+        <is>
+          <t>Alejandro Fontan</t>
+        </is>
+      </c>
+      <c r="N42" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O42" s="21" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="P42" s="21" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="Q42" s="21" t="inlineStr"/>
+      <c r="R42" s="21" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="S42" s="21" t="inlineStr">
         <is>
           <t>Standard YouTube License</t>
         </is>
@@ -4310,10 +4686,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId75"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId83"/>
   </tableParts>
 </worksheet>
 </file>